--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gccprod.sharepoint.com/sites/YTPOOutreach/Shared Documents/Internship Recruitment/FY2026 Cycle 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gccprod-my.sharepoint.com/personal/khalisah_mahfud_from_tp_tech_gov_sg/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE0F550A-FF70-4329-AC23-722D6F72EB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{AE0F550A-FF70-4329-AC23-722D6F72EB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2D41B9-99D1-4EAC-810E-6A4441F78937}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="2" r:id="rId1"/>
@@ -47,12 +47,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1021">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1022">
   <si>
     <t xml:space="preserve">GovTech Internship Role / Project Listing </t>
-  </si>
-  <si>
-    <t>(updated as of 25th Feb 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Instructions for Applicants: </t>
@@ -4225,6 +4222,12 @@
   </si>
   <si>
     <t>1. Demonstrate self-learning ability, exploring new technologies. 2. Demonstrate strong understanding in underlying mechanism of technologies, e.g. assembly, operating systems, and coding frameworks 3. Demonstrate confidence in coding</t>
+  </si>
+  <si>
+    <t>3 months; 6 months</t>
+  </si>
+  <si>
+    <t>(updated as of 3rd March 2026)</t>
   </si>
 </sst>
 </file>
@@ -4477,6 +4480,86 @@
   </cellStyles>
   <dxfs count="96">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4508,16 +4591,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4662,16 +4735,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4703,16 +4766,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4781,26 +4834,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4833,36 +4866,6 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -4877,153 +4880,153 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}" name="Table36" displayName="Table36" ref="A1:I89" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}" name="Table36" displayName="Table36" ref="A1:I89" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:I89" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{0748C68D-1981-426F-86C2-92A762F30FB2}" name="Role" dataDxfId="90"/>
-    <tableColumn id="31" xr3:uid="{EC98935D-A715-4BC3-8622-B02D6461CBBB}" name="Internship Level" dataDxfId="89"/>
-    <tableColumn id="32" xr3:uid="{D02142C2-AA8B-4EC7-B547-DB3B4A42EC58}" name="Internship Period" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{57099192-31B2-47F7-B6E8-F6F9CDA06E90}" name="Division" dataDxfId="87"/>
-    <tableColumn id="34" xr3:uid="{56F777F3-12EB-4E2A-9BDE-AF54F0244EB8}" name="Project Title" dataDxfId="86"/>
-    <tableColumn id="35" xr3:uid="{78B2F72D-A9EB-483E-84C8-3CF9D20483D2}" name="Project Description" dataDxfId="85"/>
-    <tableColumn id="36" xr3:uid="{75AF0841-CBC4-4752-814B-CFB468DE7323}" name="Learning Outcomes from Project" dataDxfId="84"/>
-    <tableColumn id="37" xr3:uid="{078FF9AA-053E-4B7E-8827-CDF83E3C8C46}" name="Prerequisites" dataDxfId="83"/>
-    <tableColumn id="38" xr3:uid="{E24322CF-5FF1-4377-9FB1-D7C53DF96F9E}" name="Work Location" dataDxfId="82"/>
+    <tableColumn id="33" xr3:uid="{0748C68D-1981-426F-86C2-92A762F30FB2}" name="Role" dataDxfId="93"/>
+    <tableColumn id="31" xr3:uid="{EC98935D-A715-4BC3-8622-B02D6461CBBB}" name="Internship Level" dataDxfId="92"/>
+    <tableColumn id="32" xr3:uid="{D02142C2-AA8B-4EC7-B547-DB3B4A42EC58}" name="Internship Period" dataDxfId="91"/>
+    <tableColumn id="6" xr3:uid="{57099192-31B2-47F7-B6E8-F6F9CDA06E90}" name="Division" dataDxfId="90"/>
+    <tableColumn id="34" xr3:uid="{56F777F3-12EB-4E2A-9BDE-AF54F0244EB8}" name="Project Title" dataDxfId="89"/>
+    <tableColumn id="35" xr3:uid="{78B2F72D-A9EB-483E-84C8-3CF9D20483D2}" name="Project Description" dataDxfId="88"/>
+    <tableColumn id="36" xr3:uid="{75AF0841-CBC4-4752-814B-CFB468DE7323}" name="Learning Outcomes from Project" dataDxfId="87"/>
+    <tableColumn id="37" xr3:uid="{078FF9AA-053E-4B7E-8827-CDF83E3C8C46}" name="Prerequisites" dataDxfId="86"/>
+    <tableColumn id="38" xr3:uid="{E24322CF-5FF1-4377-9FB1-D7C53DF96F9E}" name="Work Location" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}" name="Table31012" displayName="Table31012" ref="A1:I16" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}" name="Table31012" displayName="Table31012" ref="A1:I16" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
   <autoFilter ref="A1:I16" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{1137FCED-CBA2-456D-B999-1E095510DC83}" name="Role" dataDxfId="77"/>
-    <tableColumn id="31" xr3:uid="{CE2FD7C7-A6FE-482D-B26D-F3AD95E4514B}" name="Internship Level" dataDxfId="76"/>
-    <tableColumn id="32" xr3:uid="{DD832103-8BCC-4978-81EC-CB2942E1BBEA}" name="Internship Period" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{F6E9DF75-BDF4-4C0D-8A9A-94D620D819F1}" name="Division" dataDxfId="74"/>
-    <tableColumn id="34" xr3:uid="{102DA629-B2A1-47C5-BD96-B1C4D3590678}" name="Project Title" dataDxfId="73"/>
-    <tableColumn id="35" xr3:uid="{DD6D10D5-B166-463F-B325-238170808A01}" name="Project Description" dataDxfId="72"/>
-    <tableColumn id="36" xr3:uid="{67E906FE-1632-4149-81AF-BAB95CF37AFA}" name="Learning Outcomes from Project" dataDxfId="71"/>
-    <tableColumn id="37" xr3:uid="{AC0FA0FB-D199-4162-9146-D3AF40F5E0F5}" name="Prerequisites" dataDxfId="70"/>
-    <tableColumn id="1" xr3:uid="{BCFA29C5-1C32-4F12-BCA5-5674DFA48E1D}" name="Work Location" dataDxfId="69"/>
+    <tableColumn id="33" xr3:uid="{1137FCED-CBA2-456D-B999-1E095510DC83}" name="Role" dataDxfId="82"/>
+    <tableColumn id="31" xr3:uid="{CE2FD7C7-A6FE-482D-B26D-F3AD95E4514B}" name="Internship Level" dataDxfId="81"/>
+    <tableColumn id="32" xr3:uid="{DD832103-8BCC-4978-81EC-CB2942E1BBEA}" name="Internship Period" dataDxfId="80"/>
+    <tableColumn id="6" xr3:uid="{F6E9DF75-BDF4-4C0D-8A9A-94D620D819F1}" name="Division" dataDxfId="79"/>
+    <tableColumn id="34" xr3:uid="{102DA629-B2A1-47C5-BD96-B1C4D3590678}" name="Project Title" dataDxfId="78"/>
+    <tableColumn id="35" xr3:uid="{DD6D10D5-B166-463F-B325-238170808A01}" name="Project Description" dataDxfId="77"/>
+    <tableColumn id="36" xr3:uid="{67E906FE-1632-4149-81AF-BAB95CF37AFA}" name="Learning Outcomes from Project" dataDxfId="76"/>
+    <tableColumn id="37" xr3:uid="{AC0FA0FB-D199-4162-9146-D3AF40F5E0F5}" name="Prerequisites" dataDxfId="75"/>
+    <tableColumn id="1" xr3:uid="{BCFA29C5-1C32-4F12-BCA5-5674DFA48E1D}" name="Work Location" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}" name="Table31015" displayName="Table31015" ref="A1:I11" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}" name="Table31015" displayName="Table31015" ref="A1:I11" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
   <autoFilter ref="A1:I11" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{B55C53FF-7311-43DB-8F0C-30BBF5307241}" name="Role" dataDxfId="66"/>
-    <tableColumn id="31" xr3:uid="{B79C9A8B-E883-4C53-8AC0-6A22A68E42A9}" name="Internship Level" dataDxfId="65"/>
-    <tableColumn id="32" xr3:uid="{20E57068-0292-44A0-AF06-837B65A1F2AE}" name="Internship Period" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{1E58FE47-A1E1-4995-A1A5-DE9D2BB6E685}" name="Division" dataDxfId="63"/>
-    <tableColumn id="34" xr3:uid="{16BDF488-D6F5-4530-AA3E-1DDD138BA52E}" name="Project Title" dataDxfId="62"/>
-    <tableColumn id="35" xr3:uid="{DB6F356B-C114-434D-8314-212663E980F3}" name="Project Description" dataDxfId="61"/>
-    <tableColumn id="36" xr3:uid="{C15C0B20-7E4C-4681-A108-F7605A5C1FFD}" name="Learning Outcomes from Project" dataDxfId="60"/>
-    <tableColumn id="37" xr3:uid="{A40FB19E-D746-4220-9068-7B734732BE34}" name="Prerequisites" dataDxfId="59"/>
-    <tableColumn id="1" xr3:uid="{175BBD9F-C7E8-4BD1-B6C4-CEEBD0B846D2}" name="Work Location" dataDxfId="58"/>
+    <tableColumn id="33" xr3:uid="{B55C53FF-7311-43DB-8F0C-30BBF5307241}" name="Role" dataDxfId="71"/>
+    <tableColumn id="31" xr3:uid="{B79C9A8B-E883-4C53-8AC0-6A22A68E42A9}" name="Internship Level" dataDxfId="70"/>
+    <tableColumn id="32" xr3:uid="{20E57068-0292-44A0-AF06-837B65A1F2AE}" name="Internship Period" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{1E58FE47-A1E1-4995-A1A5-DE9D2BB6E685}" name="Division" dataDxfId="68"/>
+    <tableColumn id="34" xr3:uid="{16BDF488-D6F5-4530-AA3E-1DDD138BA52E}" name="Project Title" dataDxfId="67"/>
+    <tableColumn id="35" xr3:uid="{DB6F356B-C114-434D-8314-212663E980F3}" name="Project Description" dataDxfId="66"/>
+    <tableColumn id="36" xr3:uid="{C15C0B20-7E4C-4681-A108-F7605A5C1FFD}" name="Learning Outcomes from Project" dataDxfId="65"/>
+    <tableColumn id="37" xr3:uid="{A40FB19E-D746-4220-9068-7B734732BE34}" name="Prerequisites" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{175BBD9F-C7E8-4BD1-B6C4-CEEBD0B846D2}" name="Work Location" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}" name="Table310143" displayName="Table310143" ref="A1:I14" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}" name="Table310143" displayName="Table310143" ref="A1:I14" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
   <autoFilter ref="A1:I14" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{52C17D36-200E-47A8-A5A7-56415E42EBB9}" name="Role" dataDxfId="54"/>
-    <tableColumn id="31" xr3:uid="{4F4AF139-EDBA-4117-A886-0E8CD7BE76AA}" name="Internship Level" dataDxfId="53"/>
-    <tableColumn id="32" xr3:uid="{B64954E1-D9DD-4CB2-971C-A0ACDBA2776D}" name="Internship Period" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{0C87C0DB-61D9-47F5-8696-7411967EB928}" name="Division" dataDxfId="51"/>
-    <tableColumn id="34" xr3:uid="{C04740A6-C749-4E65-BE04-4E5C14A9ADED}" name="Project Title" dataDxfId="50"/>
-    <tableColumn id="35" xr3:uid="{11CA7598-5645-4FEB-9530-6C74D6D10480}" name="Project Description" dataDxfId="49"/>
-    <tableColumn id="36" xr3:uid="{9CBED2FF-C29F-40A0-B74E-A2F732E64748}" name="Learning Outcomes from Project" dataDxfId="48"/>
-    <tableColumn id="37" xr3:uid="{88C64C2E-E972-4F9A-9B67-78DD013E62BE}" name="Prerequisites" dataDxfId="47"/>
-    <tableColumn id="1" xr3:uid="{A8D98110-5147-48DD-AC7E-4E46154FF1C5}" name="Work Location" dataDxfId="46"/>
+    <tableColumn id="33" xr3:uid="{52C17D36-200E-47A8-A5A7-56415E42EBB9}" name="Role" dataDxfId="60"/>
+    <tableColumn id="31" xr3:uid="{4F4AF139-EDBA-4117-A886-0E8CD7BE76AA}" name="Internship Level" dataDxfId="59"/>
+    <tableColumn id="32" xr3:uid="{B64954E1-D9DD-4CB2-971C-A0ACDBA2776D}" name="Internship Period" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{0C87C0DB-61D9-47F5-8696-7411967EB928}" name="Division" dataDxfId="57"/>
+    <tableColumn id="34" xr3:uid="{C04740A6-C749-4E65-BE04-4E5C14A9ADED}" name="Project Title" dataDxfId="56"/>
+    <tableColumn id="35" xr3:uid="{11CA7598-5645-4FEB-9530-6C74D6D10480}" name="Project Description" dataDxfId="55"/>
+    <tableColumn id="36" xr3:uid="{9CBED2FF-C29F-40A0-B74E-A2F732E64748}" name="Learning Outcomes from Project" dataDxfId="54"/>
+    <tableColumn id="37" xr3:uid="{88C64C2E-E972-4F9A-9B67-78DD013E62BE}" name="Prerequisites" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{A8D98110-5147-48DD-AC7E-4E46154FF1C5}" name="Work Location" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}" name="Table310" displayName="Table310" ref="A1:I12" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}" name="Table310" displayName="Table310" ref="A1:I12" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:I12" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{179F0419-E40B-49A9-A4B5-7C885B75C259}" name="Role" dataDxfId="42"/>
-    <tableColumn id="31" xr3:uid="{1535E6FC-2CCA-4755-AFAA-7125F101F059}" name="Internship Level" dataDxfId="41"/>
-    <tableColumn id="32" xr3:uid="{069BC510-4225-4BD0-8E38-0CF791EE428B}" name="Internship Period" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{D7895101-2DA6-4608-8F21-8924912ABAFE}" name="Division" dataDxfId="39"/>
-    <tableColumn id="34" xr3:uid="{6F41430F-AFB4-48B3-8236-636411C20E38}" name="Project Title" dataDxfId="38"/>
-    <tableColumn id="35" xr3:uid="{45623342-32AD-495F-B0B4-C5B71DD6D7D0}" name="Project Description" dataDxfId="37"/>
-    <tableColumn id="36" xr3:uid="{26BC9F46-2F13-40BC-8BD3-CC41CA86A8B7}" name="Learning Outcomes from Project" dataDxfId="36"/>
-    <tableColumn id="37" xr3:uid="{09CAC57D-6B7C-4EE7-925C-8FE36490D467}" name="Prerequisites" dataDxfId="35"/>
-    <tableColumn id="1" xr3:uid="{B9916A29-2AED-410A-8A64-EB79C7F535CE}" name="Work Location" dataDxfId="34"/>
+    <tableColumn id="33" xr3:uid="{179F0419-E40B-49A9-A4B5-7C885B75C259}" name="Role" dataDxfId="49"/>
+    <tableColumn id="31" xr3:uid="{1535E6FC-2CCA-4755-AFAA-7125F101F059}" name="Internship Level" dataDxfId="48"/>
+    <tableColumn id="32" xr3:uid="{069BC510-4225-4BD0-8E38-0CF791EE428B}" name="Internship Period" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{D7895101-2DA6-4608-8F21-8924912ABAFE}" name="Division" dataDxfId="46"/>
+    <tableColumn id="34" xr3:uid="{6F41430F-AFB4-48B3-8236-636411C20E38}" name="Project Title" dataDxfId="45"/>
+    <tableColumn id="35" xr3:uid="{45623342-32AD-495F-B0B4-C5B71DD6D7D0}" name="Project Description" dataDxfId="44"/>
+    <tableColumn id="36" xr3:uid="{26BC9F46-2F13-40BC-8BD3-CC41CA86A8B7}" name="Learning Outcomes from Project" dataDxfId="43"/>
+    <tableColumn id="37" xr3:uid="{09CAC57D-6B7C-4EE7-925C-8FE36490D467}" name="Prerequisites" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{B9916A29-2AED-410A-8A64-EB79C7F535CE}" name="Work Location" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}" name="Table3" displayName="Table3" ref="A1:I26" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}" name="Table3" displayName="Table3" ref="A1:I26" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:I26" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{07DAB1D9-0161-41A3-9D95-34B91970F6D8}" name="Role" dataDxfId="31"/>
-    <tableColumn id="31" xr3:uid="{2FA4251D-12E8-4A4C-B4F3-14C845C15D49}" name="Internship Level" dataDxfId="30"/>
-    <tableColumn id="32" xr3:uid="{8334EE4E-375B-4677-A463-460E8B581C2D}" name="Internship Period" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{CF5DEC58-A35F-42A8-9B88-F1113285F072}" name="Division" dataDxfId="28"/>
-    <tableColumn id="34" xr3:uid="{D7A6FA11-9915-4CD2-88CF-9657D87EADA4}" name="Project Title" dataDxfId="27"/>
-    <tableColumn id="35" xr3:uid="{AA414369-FB84-4884-9B83-3822BCA1179D}" name="Project Description" dataDxfId="26"/>
-    <tableColumn id="36" xr3:uid="{E7A40EE2-7914-454B-BD8C-CF219B4C4A1B}" name="Learning Outcomes from Project" dataDxfId="25"/>
-    <tableColumn id="37" xr3:uid="{40241EEC-E88D-4A0C-B493-062B7F500182}" name="Prerequisites" dataDxfId="24"/>
-    <tableColumn id="1" xr3:uid="{B21C2D4B-1A24-4050-A8E0-997BCFB44AE8}" name="Work Location" dataDxfId="23"/>
+    <tableColumn id="33" xr3:uid="{07DAB1D9-0161-41A3-9D95-34B91970F6D8}" name="Role" dataDxfId="38"/>
+    <tableColumn id="31" xr3:uid="{2FA4251D-12E8-4A4C-B4F3-14C845C15D49}" name="Internship Level" dataDxfId="37"/>
+    <tableColumn id="32" xr3:uid="{8334EE4E-375B-4677-A463-460E8B581C2D}" name="Internship Period" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{CF5DEC58-A35F-42A8-9B88-F1113285F072}" name="Division" dataDxfId="35"/>
+    <tableColumn id="34" xr3:uid="{D7A6FA11-9915-4CD2-88CF-9657D87EADA4}" name="Project Title" dataDxfId="34"/>
+    <tableColumn id="35" xr3:uid="{AA414369-FB84-4884-9B83-3822BCA1179D}" name="Project Description" dataDxfId="33"/>
+    <tableColumn id="36" xr3:uid="{E7A40EE2-7914-454B-BD8C-CF219B4C4A1B}" name="Learning Outcomes from Project" dataDxfId="32"/>
+    <tableColumn id="37" xr3:uid="{40241EEC-E88D-4A0C-B493-062B7F500182}" name="Prerequisites" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{B21C2D4B-1A24-4050-A8E0-997BCFB44AE8}" name="Work Location" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}" name="Table31013" displayName="Table31013" ref="A1:I32" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}" name="Table31013" displayName="Table31013" ref="A1:I32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A1:I32" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{ADAD7CF3-9F65-47B1-86F1-BE3883188D10}" name="Role" dataDxfId="20"/>
-    <tableColumn id="31" xr3:uid="{1D7C1852-5EE8-43B9-A2D0-AFE5498F7C63}" name="Internship Level" dataDxfId="19"/>
-    <tableColumn id="32" xr3:uid="{C38FC37D-6B90-4DBC-8B22-30C73FB7E78F}" name="Internship Period" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{9C443B60-077D-430B-BA97-755EB594A1E1}" name="Division" dataDxfId="17"/>
-    <tableColumn id="34" xr3:uid="{C98D5E66-0F58-4CC1-BDF1-F0CD7D87CF9C}" name="Project Title" dataDxfId="16"/>
-    <tableColumn id="35" xr3:uid="{131629FC-1E47-4368-B7CD-85F89FF9D2BF}" name="Project Description" dataDxfId="15"/>
-    <tableColumn id="36" xr3:uid="{D65A7B37-B058-4C47-87D8-7038D5A150D3}" name="Learning Outcomes from Project" dataDxfId="14"/>
-    <tableColumn id="37" xr3:uid="{8294E7D5-FD11-4F40-A3FA-30B0AC6C73CF}" name="Prerequisites" dataDxfId="13"/>
-    <tableColumn id="1" xr3:uid="{068376EE-C48C-447A-9755-DE55ADB04FC5}" name="Work Location (FormSG)" dataDxfId="12"/>
+    <tableColumn id="33" xr3:uid="{ADAD7CF3-9F65-47B1-86F1-BE3883188D10}" name="Role" dataDxfId="27"/>
+    <tableColumn id="31" xr3:uid="{1D7C1852-5EE8-43B9-A2D0-AFE5498F7C63}" name="Internship Level" dataDxfId="26"/>
+    <tableColumn id="32" xr3:uid="{C38FC37D-6B90-4DBC-8B22-30C73FB7E78F}" name="Internship Period" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{9C443B60-077D-430B-BA97-755EB594A1E1}" name="Division" dataDxfId="24"/>
+    <tableColumn id="34" xr3:uid="{C98D5E66-0F58-4CC1-BDF1-F0CD7D87CF9C}" name="Project Title" dataDxfId="23"/>
+    <tableColumn id="35" xr3:uid="{131629FC-1E47-4368-B7CD-85F89FF9D2BF}" name="Project Description" dataDxfId="22"/>
+    <tableColumn id="36" xr3:uid="{D65A7B37-B058-4C47-87D8-7038D5A150D3}" name="Learning Outcomes from Project" dataDxfId="21"/>
+    <tableColumn id="37" xr3:uid="{8294E7D5-FD11-4F40-A3FA-30B0AC6C73CF}" name="Prerequisites" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{068376EE-C48C-447A-9755-DE55ADB04FC5}" name="Work Location (FormSG)" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}" name="Table31016" displayName="Table31016" ref="A1:I5" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}" name="Table31016" displayName="Table31016" ref="A1:I5" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:I5" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{DA95D0AA-FB62-4B70-A800-88F930027C34}" name="Role" dataDxfId="8"/>
-    <tableColumn id="31" xr3:uid="{8E2FF570-713F-4DB5-988B-05A7C30FAFB3}" name="Internship Level" dataDxfId="7"/>
-    <tableColumn id="32" xr3:uid="{464B50A7-A89C-4909-B713-BF4F1C4135B4}" name="Internship Period" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{78F66A91-700B-442F-A6BD-6CE3D5107534}" name="Division" dataDxfId="5"/>
-    <tableColumn id="34" xr3:uid="{B458784E-378C-4CCD-BD09-D53D5B77407A}" name="Project Title" dataDxfId="4"/>
-    <tableColumn id="35" xr3:uid="{30B3A4A5-74EB-4F83-B8AD-928A5AF98DCE}" name="Project Description" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{E55669FF-2098-4AD3-ABA2-9B535069A7B9}" name="Learning Outcomes from Project" dataDxfId="2"/>
-    <tableColumn id="37" xr3:uid="{65FC8008-BE3F-412D-BB33-14DEC1FAA16B}" name="Prerequisites" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{D8FD8DAE-DD25-4B67-8930-CC786B7B5D99}" name="Work Location" dataDxfId="0"/>
+    <tableColumn id="33" xr3:uid="{DA95D0AA-FB62-4B70-A800-88F930027C34}" name="Role" dataDxfId="16"/>
+    <tableColumn id="31" xr3:uid="{8E2FF570-713F-4DB5-988B-05A7C30FAFB3}" name="Internship Level" dataDxfId="15"/>
+    <tableColumn id="32" xr3:uid="{464B50A7-A89C-4909-B713-BF4F1C4135B4}" name="Internship Period" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{78F66A91-700B-442F-A6BD-6CE3D5107534}" name="Division" dataDxfId="13"/>
+    <tableColumn id="34" xr3:uid="{B458784E-378C-4CCD-BD09-D53D5B77407A}" name="Project Title" dataDxfId="12"/>
+    <tableColumn id="35" xr3:uid="{30B3A4A5-74EB-4F83-B8AD-928A5AF98DCE}" name="Project Description" dataDxfId="11"/>
+    <tableColumn id="36" xr3:uid="{E55669FF-2098-4AD3-ABA2-9B535069A7B9}" name="Learning Outcomes from Project" dataDxfId="10"/>
+    <tableColumn id="37" xr3:uid="{65FC8008-BE3F-412D-BB33-14DEC1FAA16B}" name="Prerequisites" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{D8FD8DAE-DD25-4B67-8930-CC786B7B5D99}" name="Work Location" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5061,7 +5064,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5167,7 +5170,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5309,7 +5312,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5318,11 +5321,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9D4452-6B68-410D-A94F-ED003A775C8F}">
   <dimension ref="B1:B22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="5"/>
+    <col min="1" max="1" width="8.7265625" style="5"/>
     <col min="2" max="2" width="99" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" style="5"/>
+    <col min="3" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" s="2" customFormat="1" ht="21">
@@ -5332,34 +5335,34 @@
     </row>
     <row r="2" spans="2:2" s="2" customFormat="1" ht="13.5" customHeight="1">
       <c r="B2" s="3" t="s">
-        <v>1</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="360" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="7" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="8" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="9" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="10" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="11" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="12" spans="2:2" ht="14.45" customHeight="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="7" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="8" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="9" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="10" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="11" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="12" spans="2:2" ht="14.5" customHeight="1"/>
     <row r="13" spans="2:2" ht="15" customHeight="1"/>
-    <row r="14" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="15" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="16" spans="2:2" ht="14.45" customHeight="1"/>
-    <row r="17" ht="14.45" customHeight="1"/>
-    <row r="18" ht="14.45" customHeight="1"/>
-    <row r="19" ht="14.45" customHeight="1"/>
-    <row r="21" ht="14.45" customHeight="1"/>
+    <row r="14" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="15" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="16" spans="2:2" ht="14.5" customHeight="1"/>
+    <row r="17" ht="14.5" customHeight="1"/>
+    <row r="18" ht="14.5" customHeight="1"/>
+    <row r="19" ht="14.5" customHeight="1"/>
+    <row r="21" ht="14.5" customHeight="1"/>
     <row r="22" ht="69" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -5371,2604 +5374,2604 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB8B7AC-F5FC-46C4-BB11-51E2956519D3}">
   <dimension ref="A1:I89"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.1" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="46.85546875" style="7"/>
-    <col min="3" max="5" width="46.85546875" style="8"/>
-    <col min="7" max="7" width="46.85546875" style="7"/>
-    <col min="8" max="16384" width="46.85546875" style="8"/>
+    <col min="2" max="2" width="46.81640625" style="7"/>
+    <col min="3" max="5" width="46.81640625" style="8"/>
+    <col min="7" max="7" width="46.81640625" style="7"/>
+    <col min="8" max="16384" width="46.81640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35.1" customHeight="1">
+    <row r="1" spans="1:9" ht="35.15" customHeight="1">
       <c r="A1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="I2" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>26</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="I7" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>72</v>
-      </c>
       <c r="I11" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="H12" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>77</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="H13" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="H15" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="I15" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1">
       <c r="A16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="H16" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>100</v>
-      </c>
       <c r="I16" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="G17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="H17" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>106</v>
-      </c>
       <c r="I17" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="H18" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>112</v>
-      </c>
       <c r="I18" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="G19" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="I19" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="G20" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="H20" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>122</v>
-      </c>
       <c r="I20" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="G21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="H21" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>128</v>
-      </c>
       <c r="I21" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="G22" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="H22" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>134</v>
-      </c>
       <c r="I22" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="F23" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="G23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="H23" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>140</v>
-      </c>
       <c r="I23" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="I24" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="G25" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="H25" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="I25" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="9" t="s">
+      <c r="F26" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="G26" t="s">
         <v>155</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>156</v>
       </c>
-      <c r="H26" t="s">
-        <v>157</v>
-      </c>
       <c r="I26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="39.75" customHeight="1">
       <c r="A27" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>160</v>
-      </c>
       <c r="G27" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" t="s">
         <v>156</v>
       </c>
-      <c r="H27" t="s">
-        <v>157</v>
-      </c>
       <c r="I27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.75" customHeight="1">
       <c r="A28" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="F28" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="G28" t="s">
         <v>163</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>164</v>
       </c>
-      <c r="H28" t="s">
-        <v>165</v>
-      </c>
       <c r="I28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.75" customHeight="1">
       <c r="A29" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="C29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="G29" t="s">
         <v>170</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>171</v>
       </c>
-      <c r="H29" t="s">
-        <v>172</v>
-      </c>
       <c r="I29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.75" customHeight="1">
       <c r="A30" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" s="9" t="s">
+      <c r="F30" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="G30" t="s">
         <v>175</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>176</v>
       </c>
-      <c r="H30" t="s">
-        <v>177</v>
-      </c>
       <c r="I30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.75" customHeight="1">
       <c r="A31" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" s="9" t="s">
+      <c r="F31" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="G31" t="s">
         <v>180</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>181</v>
       </c>
-      <c r="H31" t="s">
-        <v>182</v>
-      </c>
       <c r="I31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.75" customHeight="1">
       <c r="A32" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="G32" t="s">
         <v>185</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>186</v>
       </c>
-      <c r="H32" t="s">
-        <v>187</v>
-      </c>
       <c r="I32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="39.75" customHeight="1">
       <c r="A33" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="G33" t="s">
         <v>190</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>191</v>
       </c>
-      <c r="H33" t="s">
-        <v>192</v>
-      </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="39.75" customHeight="1">
       <c r="A34" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" s="9" t="s">
+      <c r="F34" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="G34" t="s">
         <v>195</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>196</v>
       </c>
-      <c r="H34" t="s">
-        <v>197</v>
-      </c>
       <c r="I34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="39.75" customHeight="1">
       <c r="A35" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="G35" t="s">
         <v>200</v>
       </c>
-      <c r="G35" t="s">
-        <v>201</v>
-      </c>
       <c r="H35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="39.75" customHeight="1">
       <c r="A36" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="G36" t="s">
         <v>204</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>205</v>
       </c>
-      <c r="H36" t="s">
-        <v>206</v>
-      </c>
       <c r="I36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="39.75" customHeight="1">
       <c r="A37" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" s="10" t="s">
+      <c r="F37" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="G37" t="s">
         <v>209</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>210</v>
       </c>
-      <c r="H37" t="s">
-        <v>211</v>
-      </c>
       <c r="I37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="39.75" customHeight="1">
       <c r="A38" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="E38" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="F38" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="G38" t="s">
         <v>215</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>216</v>
       </c>
-      <c r="H38" t="s">
-        <v>217</v>
-      </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="39.75" customHeight="1">
       <c r="A39" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="G39" t="s">
         <v>220</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>221</v>
       </c>
-      <c r="H39" t="s">
-        <v>222</v>
-      </c>
       <c r="I39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="39.75" customHeight="1">
       <c r="A40" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="G40" t="s">
         <v>225</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>226</v>
       </c>
-      <c r="H40" t="s">
-        <v>227</v>
-      </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="39.75" customHeight="1">
       <c r="A41" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E41" s="9" t="s">
+      <c r="F41" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="G41" t="s">
         <v>230</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>231</v>
       </c>
-      <c r="H41" t="s">
-        <v>232</v>
-      </c>
       <c r="I41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="39.75" customHeight="1">
       <c r="A42" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E42" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E42" s="9" t="s">
+      <c r="F42" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="G42" t="s">
         <v>235</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>236</v>
       </c>
-      <c r="H42" t="s">
-        <v>237</v>
-      </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="39.75" customHeight="1">
       <c r="A43" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="E43" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="F43" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="G43" t="s">
         <v>242</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>243</v>
       </c>
-      <c r="H43" t="s">
-        <v>244</v>
-      </c>
       <c r="I43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="39.75" customHeight="1">
       <c r="A44" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E44" s="9" t="s">
+      <c r="F44" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="G44" t="s">
         <v>247</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>248</v>
       </c>
-      <c r="H44" t="s">
-        <v>249</v>
-      </c>
       <c r="I44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="39.75" customHeight="1">
       <c r="A45" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E45" s="9" t="s">
+      <c r="F45" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="G45" t="s">
         <v>252</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>253</v>
       </c>
-      <c r="H45" t="s">
-        <v>254</v>
-      </c>
       <c r="I45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="39.75" customHeight="1">
       <c r="A46" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B46" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E46" s="9" t="s">
+      <c r="F46" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="G46" t="s">
         <v>257</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>258</v>
       </c>
-      <c r="H46" t="s">
-        <v>259</v>
-      </c>
       <c r="I46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="39.75" customHeight="1">
       <c r="A47" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E47" s="9" t="s">
+      <c r="F47" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="G47" t="s">
         <v>262</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>263</v>
       </c>
-      <c r="H47" t="s">
-        <v>264</v>
-      </c>
       <c r="I47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="39.75" customHeight="1">
       <c r="A48" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E48" s="9" t="s">
+      <c r="F48" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="G48" t="s">
         <v>267</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>268</v>
       </c>
-      <c r="H48" t="s">
-        <v>269</v>
-      </c>
       <c r="I48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="39.75" customHeight="1">
       <c r="A49" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="G49" t="s">
         <v>272</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>273</v>
       </c>
-      <c r="H49" t="s">
-        <v>274</v>
-      </c>
       <c r="I49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="39.75" customHeight="1">
       <c r="A50" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="9" t="s">
+      <c r="E50" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="F50" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="G50" t="s">
         <v>278</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>279</v>
       </c>
-      <c r="H50" t="s">
+      <c r="I50" t="s">
         <v>280</v>
-      </c>
-      <c r="I50" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="39.75" customHeight="1">
       <c r="A51" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E51" s="9" t="s">
+      <c r="F51" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="G51" t="s">
         <v>284</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>285</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>286</v>
-      </c>
-      <c r="I51" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="39.75" customHeight="1">
       <c r="A52" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="C52" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E52" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E52" s="9" t="s">
+      <c r="F52" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="G52" t="s">
         <v>291</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>292</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
         <v>293</v>
-      </c>
-      <c r="I52" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="39.75" customHeight="1">
       <c r="A53" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E53" s="9" t="s">
+      <c r="F53" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="G53" t="s">
         <v>297</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>298</v>
       </c>
-      <c r="H53" t="s">
-        <v>299</v>
-      </c>
       <c r="I53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="39.75" customHeight="1">
       <c r="A54" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E54" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E54" s="9" t="s">
+      <c r="F54" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="G54" t="s">
         <v>302</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>303</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>304</v>
-      </c>
-      <c r="I54" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="39.75" customHeight="1">
       <c r="A55" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E55" s="9" t="s">
+      <c r="F55" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="G55" t="s">
         <v>308</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>309</v>
       </c>
-      <c r="H55" t="s">
-        <v>310</v>
-      </c>
       <c r="I55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="39.75" customHeight="1">
       <c r="A56" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E56" s="9" t="s">
+      <c r="F56" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="G56" t="s">
         <v>313</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>314</v>
       </c>
-      <c r="H56" t="s">
-        <v>315</v>
-      </c>
       <c r="I56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="39.75" customHeight="1">
       <c r="A57" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E57" s="9" t="s">
+      <c r="F57" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="G57" t="s">
         <v>318</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>319</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>320</v>
-      </c>
-      <c r="I57" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="39.75" customHeight="1">
       <c r="A58" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E58" s="9" t="s">
+      <c r="F58" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="G58" t="s">
         <v>324</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>325</v>
       </c>
-      <c r="H58" t="s">
-        <v>326</v>
-      </c>
       <c r="I58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="39.75" customHeight="1">
       <c r="A59" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="9" t="s">
+      <c r="E59" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="F59" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="G59" t="s">
         <v>330</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>331</v>
       </c>
-      <c r="H59" t="s">
-        <v>332</v>
-      </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="39.75" customHeight="1">
       <c r="A60" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E60" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="B60" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E60" s="9" t="s">
+      <c r="F60" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="G60" t="s">
         <v>335</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>336</v>
       </c>
-      <c r="H60" t="s">
-        <v>337</v>
-      </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="39.75" customHeight="1">
       <c r="A61" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E61" s="9" t="s">
+      <c r="F61" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="G61" t="s">
         <v>340</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>341</v>
       </c>
-      <c r="H61" t="s">
-        <v>342</v>
-      </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="39.75" customHeight="1">
       <c r="A62" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E62" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E62" s="9" t="s">
+      <c r="F62" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="G62" t="s">
         <v>345</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>346</v>
       </c>
-      <c r="H62" t="s">
-        <v>347</v>
-      </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="39.75" customHeight="1">
       <c r="A63" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="B63" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="G63" t="s">
         <v>350</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>351</v>
       </c>
-      <c r="H63" t="s">
-        <v>352</v>
-      </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="39.75" customHeight="1">
       <c r="A64" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="9" t="s">
+      <c r="E64" s="9" t="s">
         <v>354</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="F64" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="G64" t="s">
         <v>356</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>357</v>
       </c>
-      <c r="H64" t="s">
-        <v>358</v>
-      </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="39.75" customHeight="1">
       <c r="A65" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="9" t="s">
+      <c r="E65" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="F65" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="G65" t="s">
         <v>362</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>363</v>
       </c>
-      <c r="H65" t="s">
-        <v>364</v>
-      </c>
       <c r="I65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="39.75" customHeight="1">
       <c r="A66" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E66" s="9" t="s">
+      <c r="F66" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="G66" t="s">
         <v>367</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>368</v>
       </c>
-      <c r="H66" t="s">
-        <v>369</v>
-      </c>
       <c r="I66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="39.75" customHeight="1">
       <c r="A67" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E67" s="9" t="s">
+      <c r="F67" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="G67" t="s">
         <v>372</v>
       </c>
-      <c r="G67" t="s">
-        <v>373</v>
-      </c>
       <c r="H67" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="39.75" customHeight="1">
       <c r="A68" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="B68" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E68" s="9" t="s">
+      <c r="F68" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="G68" t="s">
         <v>376</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>377</v>
       </c>
-      <c r="H68" t="s">
-        <v>378</v>
-      </c>
       <c r="I68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="39.75" customHeight="1">
       <c r="A69" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="B69" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E69" s="9" t="s">
+      <c r="F69" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="G69" t="s">
         <v>381</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>382</v>
       </c>
-      <c r="H69" t="s">
-        <v>383</v>
-      </c>
       <c r="I69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="39.75" customHeight="1">
       <c r="A70" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="B70" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E70" s="9" t="s">
+      <c r="F70" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="G70" t="s">
         <v>386</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>387</v>
       </c>
-      <c r="H70" t="s">
-        <v>388</v>
-      </c>
       <c r="I70" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="39.75" customHeight="1">
       <c r="A71" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="B71" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E71" s="9" t="s">
+      <c r="F71" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="G71" t="s">
         <v>391</v>
       </c>
-      <c r="G71" t="s">
-        <v>392</v>
-      </c>
       <c r="H71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="39.75" customHeight="1">
       <c r="A72" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="B72" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E72" s="9" t="s">
+      <c r="F72" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="G72" t="s">
         <v>395</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>396</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
         <v>397</v>
-      </c>
-      <c r="I72" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="39.75" customHeight="1">
       <c r="A73" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="B73" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D73" s="9" t="s">
+      <c r="E73" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="F73" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="G73" t="s">
         <v>402</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>403</v>
       </c>
-      <c r="H73" t="s">
-        <v>404</v>
-      </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="39.75" customHeight="1">
       <c r="A74" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="9" t="s">
+      <c r="E74" s="9" t="s">
         <v>406</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="F74" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="G74" t="s">
         <v>408</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>409</v>
       </c>
-      <c r="H74" t="s">
-        <v>410</v>
-      </c>
       <c r="I74" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="39.75" customHeight="1">
       <c r="A75" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E75" s="9" t="s">
+      <c r="F75" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="F75" s="12" t="s">
+      <c r="G75" t="s">
         <v>413</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>414</v>
       </c>
-      <c r="H75" t="s">
-        <v>415</v>
-      </c>
       <c r="I75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="39.75" customHeight="1">
       <c r="A76" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D76" s="9" t="s">
+      <c r="E76" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E76" s="9" t="s">
+      <c r="F76" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="G76" t="s">
         <v>419</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>420</v>
       </c>
-      <c r="H76" t="s">
-        <v>421</v>
-      </c>
       <c r="I76" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="39.75" customHeight="1">
       <c r="A77" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77" s="9" t="s">
+      <c r="E77" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="E77" s="9" t="s">
+      <c r="F77" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="G77" t="s">
         <v>425</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>426</v>
       </c>
-      <c r="H77" t="s">
-        <v>427</v>
-      </c>
       <c r="I77" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="39.75" customHeight="1">
       <c r="A78" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="E78" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="E78" s="9" t="s">
+      <c r="F78" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="G78" t="s">
         <v>431</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>432</v>
       </c>
-      <c r="H78" t="s">
-        <v>433</v>
-      </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="39.75" customHeight="1">
       <c r="A79" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E79" s="9" t="s">
+      <c r="F79" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="G79" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="H79" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="H79" s="12" t="s">
-        <v>438</v>
-      </c>
       <c r="I79" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="39.75" customHeight="1">
       <c r="A80" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E80" s="9" t="s">
+      <c r="F80" s="12" t="s">
         <v>440</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="G80" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="H80" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>443</v>
-      </c>
       <c r="I80" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="39.75" customHeight="1">
       <c r="A81" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E81" s="9" t="s">
+      <c r="F81" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="G81" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="H81" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="H81" s="12" t="s">
-        <v>448</v>
-      </c>
       <c r="I81" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="39.75" customHeight="1">
       <c r="A82" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E82" s="9" t="s">
+      <c r="F82" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="G82" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="G82" s="12" t="s">
+      <c r="H82" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="H82" s="12" t="s">
-        <v>453</v>
-      </c>
       <c r="I82" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="39.75" customHeight="1">
       <c r="A83" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E83" s="9" t="s">
+      <c r="F83" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="F83" s="12" t="s">
+      <c r="G83" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="G83" s="12" t="s">
+      <c r="H83" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="H83" s="12" t="s">
-        <v>458</v>
-      </c>
       <c r="I83" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="39.75" customHeight="1">
       <c r="A84" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="C84" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="C84" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E84" s="9" t="s">
+      <c r="F84" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="G84" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="G84" s="12" t="s">
+      <c r="H84" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="H84" s="12" t="s">
-        <v>464</v>
-      </c>
       <c r="I84" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="39.75" customHeight="1">
       <c r="A85" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E85" s="9" t="s">
+      <c r="F85" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="F85" s="12" t="s">
+      <c r="G85" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="H85" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="H85" s="12" t="s">
-        <v>469</v>
-      </c>
       <c r="I85" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="39.75" customHeight="1">
       <c r="A86" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E86" s="9" t="s">
+      <c r="F86" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="G86" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="G86" s="12" t="s">
+      <c r="H86" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="H86" s="12" t="s">
-        <v>474</v>
-      </c>
       <c r="I86" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="39.75" customHeight="1">
       <c r="A87" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87" s="9" t="s">
+      <c r="E87" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="F87" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="F87" s="12" t="s">
+      <c r="G87" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="G87" s="12" t="s">
+      <c r="H87" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="H87" s="12" t="s">
-        <v>480</v>
-      </c>
       <c r="I87" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="39.75" customHeight="1">
       <c r="A88" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="B88" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="C88" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="C88" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E88" s="9" t="s">
+      <c r="F88" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="F88" s="12" t="s">
+      <c r="G88" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="G88" s="12" t="s">
+      <c r="H88" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="H88" s="12" t="s">
-        <v>486</v>
-      </c>
       <c r="I88" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="37.5" customHeight="1">
       <c r="A89" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="B89" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="9" t="s">
+      <c r="E89" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="F89" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="G89" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="H89" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="H89" s="12" t="s">
+      <c r="I89" s="9" t="s">
         <v>492</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>493</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="95" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G90:I1048576 E1:G6 F7:G7 E8:G25 E30:F36 E26:F28">
-    <cfRule type="duplicateValues" dxfId="93" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7980,35 +7983,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC78194-0EAE-4863-932E-620D6F9003D6}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8018,445 +8021,445 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>499</v>
-      </c>
       <c r="I2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>503</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>505</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>510</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>511</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>515</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>522</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>528</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>533</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>536</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>541</v>
-      </c>
       <c r="I10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>546</v>
-      </c>
       <c r="I11" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>551</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>556</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="39.75" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>559</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>561</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="39.75" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>562</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>565</v>
-      </c>
       <c r="I15" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="39.75" customHeight="1">
       <c r="A16" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>567</v>
-      </c>
       <c r="G16" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>564</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>565</v>
-      </c>
       <c r="I16" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:H7 G9:H14 E8:G8 J10:J1048576 G17:H1048576">
-    <cfRule type="duplicateValues" dxfId="80" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8470,37 +8473,37 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="9" width="46.85546875" customWidth="1"/>
-    <col min="10" max="11" width="17.42578125" customWidth="1"/>
+    <col min="1" max="9" width="46.81640625" customWidth="1"/>
+    <col min="10" max="11" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8510,31 +8513,31 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>573</v>
-      </c>
       <c r="I2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -8544,263 +8547,263 @@
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>576</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>578</v>
-      </c>
       <c r="I3" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>583</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>589</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>594</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>599</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>604</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>609</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>610</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>613</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>614</v>
-      </c>
       <c r="I10" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>618</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>619</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -8814,35 +8817,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2CB887-DB2F-4039-85A3-42E8AE0B7F48}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8852,390 +8855,390 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>625</v>
-      </c>
       <c r="I2" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="9" t="s">
         <v>631</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>637</v>
-      </c>
       <c r="I4" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="12" t="s">
         <v>639</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="H5" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="H5" s="12" t="s">
-        <v>642</v>
-      </c>
       <c r="I5" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="12" t="s">
         <v>645</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>648</v>
-      </c>
       <c r="I6" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="H7" s="12" t="s">
-        <v>655</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>660</v>
-      </c>
       <c r="I8" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>666</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>667</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>672</v>
-      </c>
       <c r="I10" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>677</v>
-      </c>
       <c r="I11" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>683</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="G13" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>688</v>
-      </c>
       <c r="I13" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="49.5" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>689</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>691</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>692</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>694</v>
-      </c>
       <c r="I14" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="14.45">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="14.5">
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:14" ht="14.45"/>
-    <row r="17" ht="14.45"/>
-    <row r="18" ht="14.45"/>
+    <row r="16" spans="1:14" ht="14.5"/>
+    <row r="17" ht="14.5"/>
+    <row r="18" ht="14.5"/>
   </sheetData>
   <conditionalFormatting sqref="E7:H13 E1:H4 F5:H6">
-    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9247,357 +9250,357 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E54D435-1138-4E19-BF53-70A1844CFEF0}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.45" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="61" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A2" s="22" t="s">
+        <v>694</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="16" t="s">
         <v>697</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>698</v>
-      </c>
       <c r="I2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A3" s="22" t="s">
+        <v>698</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>699</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>700</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>701</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="16" t="s">
         <v>702</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>703</v>
-      </c>
       <c r="I3" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A4" s="22" t="s">
+        <v>703</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>704</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="9" t="s">
         <v>707</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>708</v>
-      </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A5" s="22" t="s">
+        <v>708</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>710</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="H5" s="17" t="s">
         <v>712</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="I5" s="24" t="s">
         <v>713</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A6" s="22" t="s">
+        <v>714</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="17" t="s">
         <v>716</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>717</v>
-      </c>
       <c r="I6" s="24" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A7" s="22" t="s">
+        <v>717</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>720</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="17" t="s">
         <v>721</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>722</v>
-      </c>
       <c r="I7" s="24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A8" s="22" t="s">
+        <v>722</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>723</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>726</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>728</v>
-      </c>
       <c r="I8" s="24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A9" s="22" t="s">
+        <v>728</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>729</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>730</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="17" t="s">
         <v>732</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="I9" t="s">
         <v>733</v>
-      </c>
-      <c r="I9" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>734</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="E10" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>736</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="17" t="s">
         <v>738</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>739</v>
-      </c>
       <c r="I10" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A11" s="23" t="s">
+        <v>739</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>740</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>741</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>742</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>743</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="H11" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>745</v>
-      </c>
       <c r="I11" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A12" s="23" t="s">
+        <v>745</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>746</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>495</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>747</v>
-      </c>
       <c r="F12" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="17" t="s">
         <v>712</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="I12" s="24" t="s">
         <v>713</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="15" customHeight="1">
@@ -10089,17 +10092,17 @@
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="1:9" ht="23.45" customHeight="1">
+    <row r="111" spans="1:9" ht="23.5" customHeight="1">
       <c r="B111" s="13"/>
       <c r="F111" s="13"/>
     </row>
-    <row r="112" spans="1:9" ht="23.45" customHeight="1">
+    <row r="112" spans="1:9" ht="23.5" customHeight="1">
       <c r="B112" s="13"/>
       <c r="F112" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G6:G1048576 E1:E12">
-    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -10111,760 +10114,760 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB3264-CF9E-43B5-AED5-B1522208F209}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.45" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="72.7109375" customWidth="1"/>
+    <col min="1" max="1" width="72.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="E2" t="s">
         <v>748</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>749</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>750</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>751</v>
-      </c>
-      <c r="I2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>753</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>754</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>755</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>756</v>
       </c>
-      <c r="H3" t="s">
-        <v>757</v>
-      </c>
       <c r="I3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" t="s">
+        <v>757</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" t="s">
         <v>758</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>759</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>760</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>761</v>
       </c>
-      <c r="H4" t="s">
-        <v>762</v>
-      </c>
       <c r="I4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" t="s">
+        <v>762</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" t="s">
         <v>763</v>
       </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>764</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H5" t="s">
         <v>765</v>
       </c>
-      <c r="G5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>766</v>
-      </c>
-      <c r="I5" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.75" customHeight="1">
       <c r="A6" t="s">
+        <v>767</v>
+      </c>
+      <c r="B6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="E6" t="s">
         <v>768</v>
       </c>
-      <c r="B6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>769</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>770</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>771</v>
       </c>
-      <c r="H6" t="s">
-        <v>772</v>
-      </c>
       <c r="I6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1">
       <c r="A7" t="s">
+        <v>772</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" t="s">
         <v>773</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>774</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>775</v>
       </c>
-      <c r="H7" t="s">
-        <v>776</v>
-      </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.75" customHeight="1">
       <c r="A8" t="s">
+        <v>776</v>
+      </c>
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" t="s">
+        <v>406</v>
+      </c>
+      <c r="F8" t="s">
+        <v>407</v>
+      </c>
+      <c r="G8" t="s">
         <v>777</v>
       </c>
-      <c r="B8" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>406</v>
-      </c>
-      <c r="E8" t="s">
-        <v>407</v>
-      </c>
-      <c r="F8" t="s">
-        <v>408</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>778</v>
       </c>
-      <c r="H8" t="s">
-        <v>779</v>
-      </c>
       <c r="I8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.75" customHeight="1">
       <c r="A9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
         <v>780</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>781</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>782</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>783</v>
       </c>
-      <c r="H9" t="s">
-        <v>784</v>
-      </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.75" customHeight="1">
       <c r="A10" t="s">
+        <v>784</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
         <v>785</v>
       </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>786</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>787</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>788</v>
       </c>
-      <c r="H10" t="s">
-        <v>789</v>
-      </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.75" customHeight="1">
       <c r="A11" t="s">
+        <v>789</v>
+      </c>
+      <c r="B11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E11" t="s">
         <v>790</v>
       </c>
-      <c r="B11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>518</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>791</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>792</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>793</v>
       </c>
-      <c r="H11" t="s">
-        <v>794</v>
-      </c>
       <c r="I11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.75" customHeight="1">
       <c r="A12" t="s">
+        <v>794</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E12" t="s">
         <v>795</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>276</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>796</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>797</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>798</v>
       </c>
-      <c r="H12" t="s">
-        <v>799</v>
-      </c>
       <c r="I12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1">
       <c r="A13" t="s">
+        <v>799</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
         <v>800</v>
       </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>801</v>
       </c>
-      <c r="H13" t="s">
-        <v>802</v>
-      </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1">
       <c r="A14" t="s">
+        <v>802</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E14" t="s">
         <v>803</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>804</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>805</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>806</v>
       </c>
-      <c r="H14" t="s">
-        <v>807</v>
-      </c>
       <c r="I14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1">
       <c r="A15" t="s">
+        <v>807</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>384</v>
+      </c>
+      <c r="F15" t="s">
         <v>808</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>385</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>809</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>810</v>
       </c>
-      <c r="H15" t="s">
-        <v>811</v>
-      </c>
       <c r="I15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1">
       <c r="A16" t="s">
+        <v>811</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E16" t="s">
         <v>812</v>
       </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>360</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>813</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>814</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>815</v>
       </c>
-      <c r="H16" t="s">
-        <v>816</v>
-      </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" t="s">
+        <v>816</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" t="s">
         <v>817</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>276</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>818</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>819</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>820</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>821</v>
-      </c>
-      <c r="I17" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" t="s">
+        <v>822</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
         <v>823</v>
       </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>824</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>825</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>826</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>827</v>
       </c>
-      <c r="H18" t="s">
-        <v>828</v>
-      </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" t="s">
+        <v>828</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>275</v>
+      </c>
+      <c r="E19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" t="s">
         <v>829</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>276</v>
-      </c>
-      <c r="E19" t="s">
-        <v>301</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>830</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>831</v>
       </c>
-      <c r="H19" t="s">
-        <v>832</v>
-      </c>
       <c r="I19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" t="s">
+        <v>832</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>416</v>
+      </c>
+      <c r="E20" t="s">
+        <v>735</v>
+      </c>
+      <c r="F20" t="s">
         <v>833</v>
       </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>417</v>
-      </c>
-      <c r="E20" t="s">
-        <v>736</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>834</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>835</v>
       </c>
-      <c r="H20" t="s">
-        <v>836</v>
-      </c>
       <c r="I20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" t="s">
+        <v>836</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>568</v>
+      </c>
+      <c r="E21" t="s">
         <v>837</v>
       </c>
-      <c r="B21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>569</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>838</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>839</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>840</v>
       </c>
-      <c r="H21" t="s">
-        <v>841</v>
-      </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" t="s">
+        <v>841</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
         <v>842</v>
       </c>
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>843</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>844</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>845</v>
       </c>
-      <c r="H22" t="s">
-        <v>846</v>
-      </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" t="s">
+        <v>846</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>327</v>
+      </c>
+      <c r="E23" t="s">
         <v>847</v>
       </c>
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>328</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>848</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>849</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>850</v>
       </c>
-      <c r="H23" t="s">
-        <v>851</v>
-      </c>
       <c r="I23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" t="s">
+        <v>851</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
         <v>852</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
         <v>853</v>
       </c>
-      <c r="F24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>854</v>
       </c>
-      <c r="H24" t="s">
-        <v>855</v>
-      </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" t="s">
+        <v>855</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>475</v>
+      </c>
+      <c r="E25" t="s">
         <v>856</v>
       </c>
-      <c r="B25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>476</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>857</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>858</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>859</v>
       </c>
-      <c r="H25" t="s">
-        <v>860</v>
-      </c>
       <c r="I25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" t="s">
+        <v>860</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" t="s">
         <v>861</v>
       </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" s="25" t="s">
         <v>862</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="G26" s="25" t="s">
         <v>863</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="H26" s="25" t="s">
         <v>864</v>
       </c>
-      <c r="H26" s="25" t="s">
-        <v>865</v>
-      </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10878,38 +10881,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83D9A09-A0E5-4E5C-AE97-C199E23F008E}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="I1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -10919,31 +10922,31 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
         <v>867</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>868</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>869</v>
       </c>
-      <c r="H2" t="s">
-        <v>870</v>
-      </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -10953,872 +10956,872 @@
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" t="s">
+        <v>870</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E3" t="s">
         <v>871</v>
       </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>872</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>873</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>874</v>
       </c>
-      <c r="H3" t="s">
-        <v>875</v>
-      </c>
       <c r="I3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" t="s">
+        <v>875</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
         <v>876</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" t="s">
         <v>877</v>
       </c>
-      <c r="F4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>878</v>
       </c>
-      <c r="H4" t="s">
-        <v>879</v>
-      </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" t="s">
+        <v>879</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F5" t="s">
+        <v>407</v>
+      </c>
+      <c r="G5" t="s">
         <v>880</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>406</v>
-      </c>
-      <c r="E5" t="s">
-        <v>407</v>
-      </c>
-      <c r="F5" t="s">
-        <v>408</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>881</v>
       </c>
-      <c r="H5" t="s">
-        <v>882</v>
-      </c>
       <c r="I5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" t="s">
+        <v>882</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
         <v>883</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>884</v>
       </c>
-      <c r="H6" t="s">
-        <v>885</v>
-      </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" t="s">
+        <v>885</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E7" t="s">
+        <v>817</v>
+      </c>
+      <c r="F7" t="s">
         <v>886</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" t="s">
-        <v>818</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>887</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>888</v>
       </c>
-      <c r="H7" t="s">
-        <v>889</v>
-      </c>
       <c r="I7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" t="s">
+        <v>889</v>
+      </c>
+      <c r="B8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" t="s">
+        <v>768</v>
+      </c>
+      <c r="F8" t="s">
+        <v>769</v>
+      </c>
+      <c r="G8" t="s">
         <v>890</v>
       </c>
-      <c r="B8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>360</v>
-      </c>
-      <c r="E8" t="s">
-        <v>769</v>
-      </c>
-      <c r="F8" t="s">
-        <v>770</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>891</v>
       </c>
-      <c r="H8" t="s">
-        <v>892</v>
-      </c>
       <c r="I8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" t="s">
+        <v>892</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" t="s">
         <v>893</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>276</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>894</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>895</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>896</v>
       </c>
-      <c r="H9" t="s">
-        <v>897</v>
-      </c>
       <c r="I9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" t="s">
+        <v>897</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" t="s">
         <v>898</v>
       </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>406</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>899</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>900</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>901</v>
       </c>
-      <c r="H10" t="s">
-        <v>902</v>
-      </c>
       <c r="I10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" t="s">
+        <v>902</v>
+      </c>
+      <c r="B11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
         <v>903</v>
       </c>
-      <c r="B11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>904</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>905</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>906</v>
       </c>
-      <c r="H11" t="s">
-        <v>907</v>
-      </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" t="s">
+        <v>907</v>
+      </c>
+      <c r="B12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E12" t="s">
         <v>908</v>
       </c>
-      <c r="B12" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>909</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>910</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>911</v>
       </c>
-      <c r="H12" t="s">
-        <v>912</v>
-      </c>
       <c r="I12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" t="s">
+        <v>912</v>
+      </c>
+      <c r="B13" t="s">
         <v>913</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
         <v>914</v>
       </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>915</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>916</v>
       </c>
-      <c r="H13" t="s">
-        <v>917</v>
-      </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="39.75" customHeight="1">
       <c r="A14" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E14" t="s">
+        <v>790</v>
+      </c>
+      <c r="F14" t="s">
         <v>791</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>792</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>793</v>
       </c>
-      <c r="H14" t="s">
-        <v>794</v>
-      </c>
       <c r="I14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="39.75" customHeight="1">
       <c r="A15" t="s">
+        <v>918</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E15" t="s">
         <v>919</v>
       </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>276</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>920</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>921</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>922</v>
       </c>
-      <c r="H15" t="s">
-        <v>923</v>
-      </c>
       <c r="I15" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="39.75" customHeight="1">
       <c r="A16" t="s">
+        <v>923</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
         <v>924</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>925</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>926</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>927</v>
       </c>
-      <c r="H16" t="s">
-        <v>928</v>
-      </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" t="s">
+        <v>928</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" t="s">
         <v>929</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>930</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>931</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>932</v>
       </c>
-      <c r="H17" t="s">
-        <v>933</v>
-      </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" t="s">
+        <v>933</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" t="s">
         <v>934</v>
       </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>935</v>
       </c>
-      <c r="H18" t="s">
-        <v>936</v>
-      </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" t="s">
+        <v>936</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
         <v>937</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>938</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>939</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>940</v>
       </c>
-      <c r="H19" t="s">
-        <v>941</v>
-      </c>
       <c r="I19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" t="s">
+        <v>941</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
         <v>942</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>943</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>944</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>945</v>
       </c>
-      <c r="H20" t="s">
-        <v>946</v>
-      </c>
       <c r="I20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" t="s">
+        <v>946</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>842</v>
+      </c>
+      <c r="F21" t="s">
         <v>947</v>
       </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>843</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>948</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>949</v>
       </c>
-      <c r="H21" t="s">
-        <v>950</v>
-      </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" t="s">
+        <v>950</v>
+      </c>
+      <c r="B22" t="s">
         <v>951</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
         <v>952</v>
       </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>953</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>954</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>955</v>
       </c>
-      <c r="H22" t="s">
-        <v>956</v>
-      </c>
       <c r="I22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" t="s">
+        <v>956</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>416</v>
+      </c>
+      <c r="E23" t="s">
         <v>957</v>
       </c>
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>417</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>958</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>959</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>960</v>
       </c>
-      <c r="H23" t="s">
-        <v>961</v>
-      </c>
       <c r="I23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" t="s">
+        <v>961</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>275</v>
+      </c>
+      <c r="E24" t="s">
+        <v>300</v>
+      </c>
+      <c r="F24" t="s">
+        <v>829</v>
+      </c>
+      <c r="G24" t="s">
         <v>962</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>276</v>
-      </c>
-      <c r="E24" t="s">
-        <v>301</v>
-      </c>
-      <c r="F24" t="s">
-        <v>830</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>963</v>
       </c>
-      <c r="H24" t="s">
-        <v>964</v>
-      </c>
       <c r="I24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" t="s">
+        <v>964</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>416</v>
+      </c>
+      <c r="E25" t="s">
+        <v>417</v>
+      </c>
+      <c r="F25" t="s">
         <v>965</v>
       </c>
-      <c r="B25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>417</v>
-      </c>
-      <c r="E25" t="s">
-        <v>418</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>966</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>967</v>
       </c>
-      <c r="H25" t="s">
-        <v>968</v>
-      </c>
       <c r="I25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" t="s">
+        <v>968</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" t="s">
         <v>969</v>
       </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>970</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>971</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>972</v>
       </c>
-      <c r="H26" t="s">
-        <v>973</v>
-      </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="39.75" customHeight="1">
       <c r="A27" t="s">
+        <v>973</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" t="s">
         <v>974</v>
       </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>975</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>976</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>977</v>
       </c>
-      <c r="H27" t="s">
-        <v>978</v>
-      </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.75" customHeight="1">
       <c r="A28" t="s">
+        <v>978</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>275</v>
+      </c>
+      <c r="E28" t="s">
+        <v>322</v>
+      </c>
+      <c r="F28" t="s">
         <v>979</v>
       </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>276</v>
-      </c>
-      <c r="E28" t="s">
-        <v>323</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>980</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>981</v>
       </c>
-      <c r="H28" t="s">
-        <v>982</v>
-      </c>
       <c r="I28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.75" customHeight="1">
       <c r="A29" t="s">
+        <v>982</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" t="s">
         <v>983</v>
       </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>984</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>985</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>986</v>
       </c>
-      <c r="H29" t="s">
-        <v>987</v>
-      </c>
       <c r="I29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.75" customHeight="1">
       <c r="A30" t="s">
+        <v>987</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" t="s">
         <v>988</v>
       </c>
-      <c r="B30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>989</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>990</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>991</v>
       </c>
-      <c r="H30" t="s">
-        <v>992</v>
-      </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.75" customHeight="1">
       <c r="A31" t="s">
+        <v>992</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" t="s">
+        <v>327</v>
+      </c>
+      <c r="E31" t="s">
+        <v>333</v>
+      </c>
+      <c r="F31" t="s">
         <v>993</v>
       </c>
-      <c r="B31" t="s">
-        <v>167</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" t="s">
-        <v>328</v>
-      </c>
-      <c r="E31" t="s">
-        <v>334</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>994</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>995</v>
       </c>
-      <c r="H31" t="s">
-        <v>996</v>
-      </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.75" customHeight="1">
       <c r="A32" t="s">
+        <v>996</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>475</v>
+      </c>
+      <c r="E32" t="s">
         <v>997</v>
       </c>
-      <c r="B32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>476</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>998</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" s="9" t="s">
         <v>999</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>1000</v>
-      </c>
       <c r="H32" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -11832,160 +11835,160 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1732FC4-DAAC-4993-874D-9F36FC6B0102}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="69" customWidth="1"/>
-    <col min="9" max="9" width="76.28515625" customWidth="1"/>
+    <col min="9" max="9" width="76.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>1003</v>
-      </c>
       <c r="I2" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" s="11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>1005</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>1008</v>
-      </c>
       <c r="I3" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" s="11" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>1009</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>1011</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>1013</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>1015</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>1020</v>
-      </c>
       <c r="I5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:G5">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -11995,6 +11998,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="fdedef4e-87e2-4000-8e15-674cde7c8b45">New</Status>
+    <TaxCatchAll xmlns="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fdedef4e-87e2-4000-8e15-674cde7c8b45">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010066A22EBB8ECBC44EADCEDB9E8148A461" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="29f975ec7ee17195ec3ec33aea10547d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fdedef4e-87e2-4000-8e15-674cde7c8b45" xmlns:ns3="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e56735957132733ee79764ad374f668" ns2:_="" ns3:_="">
     <xsd:import namespace="fdedef4e-87e2-4000-8e15-674cde7c8b45"/>
@@ -12232,35 +12256,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="fdedef4e-87e2-4000-8e15-674cde7c8b45">New</Status>
-    <TaxCatchAll xmlns="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="fdedef4e-87e2-4000-8e15-674cde7c8b45">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A57F35-6032-40B6-B658-A82B5AB99034}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{068544F8-3AE0-4EEF-90C6-5DD75B425137}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553F84EA-27AD-4FBD-9707-81276D747B07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553F84EA-27AD-4FBD-9707-81276D747B07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fdedef4e-87e2-4000-8e15-674cde7c8b45"/>
+    <ds:schemaRef ds:uri="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{068544F8-3AE0-4EEF-90C6-5DD75B425137}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A57F35-6032-40B6-B658-A82B5AB99034}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="fdedef4e-87e2-4000-8e15-674cde7c8b45"/>
+    <ds:schemaRef ds:uri="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gccprod-my.sharepoint.com/personal/khalisah_mahfud_from_tp_tech_gov_sg/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gccprod.sharepoint.com/sites/YTPOOutreach/Shared Documents/Internship Recruitment/FY2026 Cycle 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{AE0F550A-FF70-4329-AC23-722D6F72EB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2D41B9-99D1-4EAC-810E-6A4441F78937}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8517D911-639E-42CF-977B-6AC297EA6C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="30990" yWindow="2055" windowWidth="14340" windowHeight="8145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="2" r:id="rId1"/>
@@ -47,9 +47,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1032">
   <si>
     <t xml:space="preserve">GovTech Internship Role / Project Listing </t>
+  </si>
+  <si>
+    <t>(updated as of 4th March 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Instructions for Applicants: </t>
@@ -374,6 +377,9 @@
     <t>Tech – Software Engineer : LTA Digital Modernisation [GDPA]</t>
   </si>
   <si>
+    <t>3 months; 6 months</t>
+  </si>
+  <si>
     <t>(Apps) Digital Society Products</t>
   </si>
   <si>
@@ -464,22 +470,25 @@
     <t>Undergraduate;Polytechnic student</t>
   </si>
   <si>
+    <t>3 months; 6 months; 12 months</t>
+  </si>
+  <si>
+    <t>Usability and Accessibility</t>
+  </si>
+  <si>
+    <t>Our U&amp;A initiative enhances the usability and accessibility of government digital services. By developing specialized tools, leading professional workshops, and creating educational resources, we champion a “shift-left” approach. Join us to drive systemic change and ensure inclusive design is integrated from day one.</t>
+  </si>
+  <si>
+    <t>- Gain hands-on development experience in crafting high-quality and maintainable code - Gain experience in working with working in cross-functional teams, communicate effectively with other functions to translate requirements into technical requirements with developers, designers and product managers. - Contribute actively to shaping the product, raise concerns, take initiative and ownership of your work just like a regular engineer. - Learn how to craft highly usable and accessible websites and the impact it has on citizens</t>
+  </si>
+  <si>
+    <t>- Knowledge in common programming languages like Javascript/Typescript, Python or Java - Knowledge in common web development and backend frameworks like React, NextJS, Fastify, Express - Knowledge in common DevOps and developer tools like Git, GitLab, CI/CD, knowledge in common cloud service providers like AWS, GCP will be a plus. - Knowledge in building LLM-powered applications will a plus.</t>
+  </si>
+  <si>
+    <t>Tech – Software Engineer : Optical [GDPP]</t>
+  </si>
+  <si>
     <t>12 months</t>
-  </si>
-  <si>
-    <t>Usability and Accessibility</t>
-  </si>
-  <si>
-    <t>Our U&amp;A initiative enhances the usability and accessibility of government digital services. By developing specialized tools, leading professional workshops, and creating educational resources, we champion a “shift-left” approach. Join us to drive systemic change and ensure inclusive design is integrated from day one.</t>
-  </si>
-  <si>
-    <t>- Gain hands-on development experience in crafting high-quality and maintainable code - Gain experience in working with working in cross-functional teams, communicate effectively with other functions to translate requirements into technical requirements with developers, designers and product managers. - Contribute actively to shaping the product, raise concerns, take initiative and ownership of your work just like a regular engineer. - Learn how to craft highly usable and accessible websites and the impact it has on citizens</t>
-  </si>
-  <si>
-    <t>- Knowledge in common programming languages like Javascript/Typescript, Python or Java - Knowledge in common web development and backend frameworks like React, NextJS, Fastify, Express - Knowledge in common DevOps and developer tools like Git, GitLab, CI/CD, knowledge in common cloud service providers like AWS, GCP will be a plus. - Knowledge in building LLM-powered applications will a plus.</t>
-  </si>
-  <si>
-    <t>Tech – Software Engineer : Optical [GDPP]</t>
   </si>
   <si>
     <t>(Platforms) Content, Insights &amp; Policy</t>
@@ -3578,6 +3587,65 @@
 5.	Comfortable with imperfect solutions: Understands that products evolve iteratively, and is willing to test, learn, and refine rather than waiting for perfect conditions before taking action.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tech – Product Manager : Innovation in Education through Human-Centred Design &amp; Digital Experimentation </t>
+  </si>
+  <si>
+    <t>Undergraduate, Polytechnic (final year)</t>
+  </si>
+  <si>
+    <t>6 months; 12 months</t>
+  </si>
+  <si>
+    <t>MOE Digital Excellence and Products Division (DXD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation in Education through Human-Centred Design &amp; Digital Experimentation </t>
+  </si>
+  <si>
+    <t>The intern will join the Digital Innovation &amp; Ventures Accelerator (DIVA) under the Digital Excellence &amp; Products Division (DXD), Ministry of Education.
+This role supports innovation projects that apply human-centred design, emerging technologies, and agile experimentation to improve teaching, learning, and administrative workflows across schools and HQ divisions.
+Key responsibilities include:
+Design &amp; Discovery
+●	Partner with HQ divisions to reframe problem statements and map current (“as-is”) versus future (“to-be”) workflows
+●	Conduct user research (interviews, journey mapping, persona development) with educators and policy teams
+●	Design and test prototypes, mockups, and lightweight digital tools
+●	Support facilitation of advisory workshops, design sprints, and co-creation sessions
+Product Pilots &amp; Implementation
+●	Support piloting and refinement of proof-of-concept solutions
+●	Track project metrics (usability feedback, efficiency gains, stakeholder satisfaction)
+●	Coordinate project logistics and documentation
+Innovation Culture Building
+●	Assist in organising hackathons, demo days, workshops, and community engagements
+●	Support outreach, participant recruitment, and stakeholder communications
+●	Co-create toolkits, templates, and one-pagers to empower grassroots innovation
+Stakeholder Engagement &amp; Capacity Building
+●	Work with educators, school leaders, and HQ officers to gather requirements and feedback
+●	Support change management efforts (communications, training reminders, adoption surveys)
+●	Develop and update training materials and knowledge artefacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By the end of the internship, the intern will:
+1.	Gain hands-on experience in human-centred design (persona development, journey mapping, co-creation facilitation).
+2.	Learn to scope, prototype, and test digital solutions within public sector constraints.
+3.	Develop stakeholder engagement and change management skills across schools and HQ divisions.
+4.	Understand innovation frameworks used in public service (design sprints, rapid prototyping, problem-framing).
+5.	Build experience supporting pilots and scaling innovation initiatives in a large government organisation.
+</t>
+  </si>
+  <si>
+    <t>●	Strong written and verbal communication skills
+●	Organised and detail-oriented; able to coordinate across multiple stakeholders
+●	Comfortable with collaboration tools (Google Workspace, Miro, Canva or equivalent)
+●	Basic analytical skills for data collection and synthesis
+Strongly Preferred:
+●	Familiarity with prototyping tools (e.g., Figma)
+●	Exposure to UX research methods or design thinking frameworks
+●	Experience supporting workshops, hackathons, or community engagements</t>
+  </si>
+  <si>
+    <t>MOE Headquarters, Singapore (On-site; may include partner school visits)</t>
+  </si>
+  <si>
     <t>Work Location (FormSG)</t>
   </si>
   <si>
@@ -4222,12 +4290,6 @@
   </si>
   <si>
     <t>1. Demonstrate self-learning ability, exploring new technologies. 2. Demonstrate strong understanding in underlying mechanism of technologies, e.g. assembly, operating systems, and coding frameworks 3. Demonstrate confidence in coding</t>
-  </si>
-  <si>
-    <t>3 months; 6 months</t>
-  </si>
-  <si>
-    <t>(updated as of 3rd March 2026)</t>
   </si>
 </sst>
 </file>
@@ -4480,86 +4542,6 @@
   </cellStyles>
   <dxfs count="96">
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4591,6 +4573,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4735,6 +4727,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4766,6 +4768,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4834,6 +4846,26 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4866,6 +4898,36 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -4880,153 +4942,153 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}" name="Table36" displayName="Table36" ref="A1:I89" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}" name="Table36" displayName="Table36" ref="A1:I89" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A1:I89" xr:uid="{D46B721B-615A-4542-9BBA-C1A27971ECB0}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{0748C68D-1981-426F-86C2-92A762F30FB2}" name="Role" dataDxfId="93"/>
-    <tableColumn id="31" xr3:uid="{EC98935D-A715-4BC3-8622-B02D6461CBBB}" name="Internship Level" dataDxfId="92"/>
-    <tableColumn id="32" xr3:uid="{D02142C2-AA8B-4EC7-B547-DB3B4A42EC58}" name="Internship Period" dataDxfId="91"/>
-    <tableColumn id="6" xr3:uid="{57099192-31B2-47F7-B6E8-F6F9CDA06E90}" name="Division" dataDxfId="90"/>
-    <tableColumn id="34" xr3:uid="{56F777F3-12EB-4E2A-9BDE-AF54F0244EB8}" name="Project Title" dataDxfId="89"/>
-    <tableColumn id="35" xr3:uid="{78B2F72D-A9EB-483E-84C8-3CF9D20483D2}" name="Project Description" dataDxfId="88"/>
-    <tableColumn id="36" xr3:uid="{75AF0841-CBC4-4752-814B-CFB468DE7323}" name="Learning Outcomes from Project" dataDxfId="87"/>
-    <tableColumn id="37" xr3:uid="{078FF9AA-053E-4B7E-8827-CDF83E3C8C46}" name="Prerequisites" dataDxfId="86"/>
-    <tableColumn id="38" xr3:uid="{E24322CF-5FF1-4377-9FB1-D7C53DF96F9E}" name="Work Location" dataDxfId="85"/>
+    <tableColumn id="33" xr3:uid="{0748C68D-1981-426F-86C2-92A762F30FB2}" name="Role" dataDxfId="90"/>
+    <tableColumn id="31" xr3:uid="{EC98935D-A715-4BC3-8622-B02D6461CBBB}" name="Internship Level" dataDxfId="89"/>
+    <tableColumn id="32" xr3:uid="{D02142C2-AA8B-4EC7-B547-DB3B4A42EC58}" name="Internship Period" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{57099192-31B2-47F7-B6E8-F6F9CDA06E90}" name="Division" dataDxfId="87"/>
+    <tableColumn id="34" xr3:uid="{56F777F3-12EB-4E2A-9BDE-AF54F0244EB8}" name="Project Title" dataDxfId="86"/>
+    <tableColumn id="35" xr3:uid="{78B2F72D-A9EB-483E-84C8-3CF9D20483D2}" name="Project Description" dataDxfId="85"/>
+    <tableColumn id="36" xr3:uid="{75AF0841-CBC4-4752-814B-CFB468DE7323}" name="Learning Outcomes from Project" dataDxfId="84"/>
+    <tableColumn id="37" xr3:uid="{078FF9AA-053E-4B7E-8827-CDF83E3C8C46}" name="Prerequisites" dataDxfId="83"/>
+    <tableColumn id="38" xr3:uid="{E24322CF-5FF1-4377-9FB1-D7C53DF96F9E}" name="Work Location" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}" name="Table31012" displayName="Table31012" ref="A1:I16" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}" name="Table31012" displayName="Table31012" ref="A1:I16" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
   <autoFilter ref="A1:I16" xr:uid="{5B5C48E8-2303-4207-94DF-2BA1143041BE}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{1137FCED-CBA2-456D-B999-1E095510DC83}" name="Role" dataDxfId="82"/>
-    <tableColumn id="31" xr3:uid="{CE2FD7C7-A6FE-482D-B26D-F3AD95E4514B}" name="Internship Level" dataDxfId="81"/>
-    <tableColumn id="32" xr3:uid="{DD832103-8BCC-4978-81EC-CB2942E1BBEA}" name="Internship Period" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{F6E9DF75-BDF4-4C0D-8A9A-94D620D819F1}" name="Division" dataDxfId="79"/>
-    <tableColumn id="34" xr3:uid="{102DA629-B2A1-47C5-BD96-B1C4D3590678}" name="Project Title" dataDxfId="78"/>
-    <tableColumn id="35" xr3:uid="{DD6D10D5-B166-463F-B325-238170808A01}" name="Project Description" dataDxfId="77"/>
-    <tableColumn id="36" xr3:uid="{67E906FE-1632-4149-81AF-BAB95CF37AFA}" name="Learning Outcomes from Project" dataDxfId="76"/>
-    <tableColumn id="37" xr3:uid="{AC0FA0FB-D199-4162-9146-D3AF40F5E0F5}" name="Prerequisites" dataDxfId="75"/>
-    <tableColumn id="1" xr3:uid="{BCFA29C5-1C32-4F12-BCA5-5674DFA48E1D}" name="Work Location" dataDxfId="74"/>
+    <tableColumn id="33" xr3:uid="{1137FCED-CBA2-456D-B999-1E095510DC83}" name="Role" dataDxfId="77"/>
+    <tableColumn id="31" xr3:uid="{CE2FD7C7-A6FE-482D-B26D-F3AD95E4514B}" name="Internship Level" dataDxfId="76"/>
+    <tableColumn id="32" xr3:uid="{DD832103-8BCC-4978-81EC-CB2942E1BBEA}" name="Internship Period" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{F6E9DF75-BDF4-4C0D-8A9A-94D620D819F1}" name="Division" dataDxfId="74"/>
+    <tableColumn id="34" xr3:uid="{102DA629-B2A1-47C5-BD96-B1C4D3590678}" name="Project Title" dataDxfId="73"/>
+    <tableColumn id="35" xr3:uid="{DD6D10D5-B166-463F-B325-238170808A01}" name="Project Description" dataDxfId="72"/>
+    <tableColumn id="36" xr3:uid="{67E906FE-1632-4149-81AF-BAB95CF37AFA}" name="Learning Outcomes from Project" dataDxfId="71"/>
+    <tableColumn id="37" xr3:uid="{AC0FA0FB-D199-4162-9146-D3AF40F5E0F5}" name="Prerequisites" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{BCFA29C5-1C32-4F12-BCA5-5674DFA48E1D}" name="Work Location" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}" name="Table31015" displayName="Table31015" ref="A1:I11" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}" name="Table31015" displayName="Table31015" ref="A1:I11" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="A1:I11" xr:uid="{484B8807-2254-4DDB-9066-9F04051FC859}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{B55C53FF-7311-43DB-8F0C-30BBF5307241}" name="Role" dataDxfId="71"/>
-    <tableColumn id="31" xr3:uid="{B79C9A8B-E883-4C53-8AC0-6A22A68E42A9}" name="Internship Level" dataDxfId="70"/>
-    <tableColumn id="32" xr3:uid="{20E57068-0292-44A0-AF06-837B65A1F2AE}" name="Internship Period" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{1E58FE47-A1E1-4995-A1A5-DE9D2BB6E685}" name="Division" dataDxfId="68"/>
-    <tableColumn id="34" xr3:uid="{16BDF488-D6F5-4530-AA3E-1DDD138BA52E}" name="Project Title" dataDxfId="67"/>
-    <tableColumn id="35" xr3:uid="{DB6F356B-C114-434D-8314-212663E980F3}" name="Project Description" dataDxfId="66"/>
-    <tableColumn id="36" xr3:uid="{C15C0B20-7E4C-4681-A108-F7605A5C1FFD}" name="Learning Outcomes from Project" dataDxfId="65"/>
-    <tableColumn id="37" xr3:uid="{A40FB19E-D746-4220-9068-7B734732BE34}" name="Prerequisites" dataDxfId="64"/>
-    <tableColumn id="1" xr3:uid="{175BBD9F-C7E8-4BD1-B6C4-CEEBD0B846D2}" name="Work Location" dataDxfId="63"/>
+    <tableColumn id="33" xr3:uid="{B55C53FF-7311-43DB-8F0C-30BBF5307241}" name="Role" dataDxfId="66"/>
+    <tableColumn id="31" xr3:uid="{B79C9A8B-E883-4C53-8AC0-6A22A68E42A9}" name="Internship Level" dataDxfId="65"/>
+    <tableColumn id="32" xr3:uid="{20E57068-0292-44A0-AF06-837B65A1F2AE}" name="Internship Period" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{1E58FE47-A1E1-4995-A1A5-DE9D2BB6E685}" name="Division" dataDxfId="63"/>
+    <tableColumn id="34" xr3:uid="{16BDF488-D6F5-4530-AA3E-1DDD138BA52E}" name="Project Title" dataDxfId="62"/>
+    <tableColumn id="35" xr3:uid="{DB6F356B-C114-434D-8314-212663E980F3}" name="Project Description" dataDxfId="61"/>
+    <tableColumn id="36" xr3:uid="{C15C0B20-7E4C-4681-A108-F7605A5C1FFD}" name="Learning Outcomes from Project" dataDxfId="60"/>
+    <tableColumn id="37" xr3:uid="{A40FB19E-D746-4220-9068-7B734732BE34}" name="Prerequisites" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{175BBD9F-C7E8-4BD1-B6C4-CEEBD0B846D2}" name="Work Location" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}" name="Table310143" displayName="Table310143" ref="A1:I14" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}" name="Table310143" displayName="Table310143" ref="A1:I14" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:I14" xr:uid="{39B878C4-4772-45B5-AAF8-A55B442C0AAE}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{52C17D36-200E-47A8-A5A7-56415E42EBB9}" name="Role" dataDxfId="60"/>
-    <tableColumn id="31" xr3:uid="{4F4AF139-EDBA-4117-A886-0E8CD7BE76AA}" name="Internship Level" dataDxfId="59"/>
-    <tableColumn id="32" xr3:uid="{B64954E1-D9DD-4CB2-971C-A0ACDBA2776D}" name="Internship Period" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{0C87C0DB-61D9-47F5-8696-7411967EB928}" name="Division" dataDxfId="57"/>
-    <tableColumn id="34" xr3:uid="{C04740A6-C749-4E65-BE04-4E5C14A9ADED}" name="Project Title" dataDxfId="56"/>
-    <tableColumn id="35" xr3:uid="{11CA7598-5645-4FEB-9530-6C74D6D10480}" name="Project Description" dataDxfId="55"/>
-    <tableColumn id="36" xr3:uid="{9CBED2FF-C29F-40A0-B74E-A2F732E64748}" name="Learning Outcomes from Project" dataDxfId="54"/>
-    <tableColumn id="37" xr3:uid="{88C64C2E-E972-4F9A-9B67-78DD013E62BE}" name="Prerequisites" dataDxfId="53"/>
-    <tableColumn id="1" xr3:uid="{A8D98110-5147-48DD-AC7E-4E46154FF1C5}" name="Work Location" dataDxfId="52"/>
+    <tableColumn id="33" xr3:uid="{52C17D36-200E-47A8-A5A7-56415E42EBB9}" name="Role" dataDxfId="54"/>
+    <tableColumn id="31" xr3:uid="{4F4AF139-EDBA-4117-A886-0E8CD7BE76AA}" name="Internship Level" dataDxfId="53"/>
+    <tableColumn id="32" xr3:uid="{B64954E1-D9DD-4CB2-971C-A0ACDBA2776D}" name="Internship Period" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{0C87C0DB-61D9-47F5-8696-7411967EB928}" name="Division" dataDxfId="51"/>
+    <tableColumn id="34" xr3:uid="{C04740A6-C749-4E65-BE04-4E5C14A9ADED}" name="Project Title" dataDxfId="50"/>
+    <tableColumn id="35" xr3:uid="{11CA7598-5645-4FEB-9530-6C74D6D10480}" name="Project Description" dataDxfId="49"/>
+    <tableColumn id="36" xr3:uid="{9CBED2FF-C29F-40A0-B74E-A2F732E64748}" name="Learning Outcomes from Project" dataDxfId="48"/>
+    <tableColumn id="37" xr3:uid="{88C64C2E-E972-4F9A-9B67-78DD013E62BE}" name="Prerequisites" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{A8D98110-5147-48DD-AC7E-4E46154FF1C5}" name="Work Location" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}" name="Table310" displayName="Table310" ref="A1:I12" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}" name="Table310" displayName="Table310" ref="A1:I12" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="A1:I12" xr:uid="{71345D43-5CF2-456D-86CB-ED149A94047F}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{179F0419-E40B-49A9-A4B5-7C885B75C259}" name="Role" dataDxfId="49"/>
-    <tableColumn id="31" xr3:uid="{1535E6FC-2CCA-4755-AFAA-7125F101F059}" name="Internship Level" dataDxfId="48"/>
-    <tableColumn id="32" xr3:uid="{069BC510-4225-4BD0-8E38-0CF791EE428B}" name="Internship Period" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{D7895101-2DA6-4608-8F21-8924912ABAFE}" name="Division" dataDxfId="46"/>
-    <tableColumn id="34" xr3:uid="{6F41430F-AFB4-48B3-8236-636411C20E38}" name="Project Title" dataDxfId="45"/>
-    <tableColumn id="35" xr3:uid="{45623342-32AD-495F-B0B4-C5B71DD6D7D0}" name="Project Description" dataDxfId="44"/>
-    <tableColumn id="36" xr3:uid="{26BC9F46-2F13-40BC-8BD3-CC41CA86A8B7}" name="Learning Outcomes from Project" dataDxfId="43"/>
-    <tableColumn id="37" xr3:uid="{09CAC57D-6B7C-4EE7-925C-8FE36490D467}" name="Prerequisites" dataDxfId="42"/>
-    <tableColumn id="1" xr3:uid="{B9916A29-2AED-410A-8A64-EB79C7F535CE}" name="Work Location" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{179F0419-E40B-49A9-A4B5-7C885B75C259}" name="Role" dataDxfId="42"/>
+    <tableColumn id="31" xr3:uid="{1535E6FC-2CCA-4755-AFAA-7125F101F059}" name="Internship Level" dataDxfId="41"/>
+    <tableColumn id="32" xr3:uid="{069BC510-4225-4BD0-8E38-0CF791EE428B}" name="Internship Period" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{D7895101-2DA6-4608-8F21-8924912ABAFE}" name="Division" dataDxfId="39"/>
+    <tableColumn id="34" xr3:uid="{6F41430F-AFB4-48B3-8236-636411C20E38}" name="Project Title" dataDxfId="38"/>
+    <tableColumn id="35" xr3:uid="{45623342-32AD-495F-B0B4-C5B71DD6D7D0}" name="Project Description" dataDxfId="37"/>
+    <tableColumn id="36" xr3:uid="{26BC9F46-2F13-40BC-8BD3-CC41CA86A8B7}" name="Learning Outcomes from Project" dataDxfId="36"/>
+    <tableColumn id="37" xr3:uid="{09CAC57D-6B7C-4EE7-925C-8FE36490D467}" name="Prerequisites" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{B9916A29-2AED-410A-8A64-EB79C7F535CE}" name="Work Location" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}" name="Table3" displayName="Table3" ref="A1:I26" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
-  <autoFilter ref="A1:I26" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}" name="Table3" displayName="Table3" ref="A1:I27" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A1:I27" xr:uid="{922D861A-3299-46BF-A181-BD1181439588}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{07DAB1D9-0161-41A3-9D95-34B91970F6D8}" name="Role" dataDxfId="38"/>
-    <tableColumn id="31" xr3:uid="{2FA4251D-12E8-4A4C-B4F3-14C845C15D49}" name="Internship Level" dataDxfId="37"/>
-    <tableColumn id="32" xr3:uid="{8334EE4E-375B-4677-A463-460E8B581C2D}" name="Internship Period" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{CF5DEC58-A35F-42A8-9B88-F1113285F072}" name="Division" dataDxfId="35"/>
-    <tableColumn id="34" xr3:uid="{D7A6FA11-9915-4CD2-88CF-9657D87EADA4}" name="Project Title" dataDxfId="34"/>
-    <tableColumn id="35" xr3:uid="{AA414369-FB84-4884-9B83-3822BCA1179D}" name="Project Description" dataDxfId="33"/>
-    <tableColumn id="36" xr3:uid="{E7A40EE2-7914-454B-BD8C-CF219B4C4A1B}" name="Learning Outcomes from Project" dataDxfId="32"/>
-    <tableColumn id="37" xr3:uid="{40241EEC-E88D-4A0C-B493-062B7F500182}" name="Prerequisites" dataDxfId="31"/>
-    <tableColumn id="1" xr3:uid="{B21C2D4B-1A24-4050-A8E0-997BCFB44AE8}" name="Work Location" dataDxfId="30"/>
+    <tableColumn id="33" xr3:uid="{07DAB1D9-0161-41A3-9D95-34B91970F6D8}" name="Role" dataDxfId="31"/>
+    <tableColumn id="31" xr3:uid="{2FA4251D-12E8-4A4C-B4F3-14C845C15D49}" name="Internship Level" dataDxfId="30"/>
+    <tableColumn id="32" xr3:uid="{8334EE4E-375B-4677-A463-460E8B581C2D}" name="Internship Period" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{CF5DEC58-A35F-42A8-9B88-F1113285F072}" name="Division" dataDxfId="28"/>
+    <tableColumn id="34" xr3:uid="{D7A6FA11-9915-4CD2-88CF-9657D87EADA4}" name="Project Title" dataDxfId="27"/>
+    <tableColumn id="35" xr3:uid="{AA414369-FB84-4884-9B83-3822BCA1179D}" name="Project Description" dataDxfId="26"/>
+    <tableColumn id="36" xr3:uid="{E7A40EE2-7914-454B-BD8C-CF219B4C4A1B}" name="Learning Outcomes from Project" dataDxfId="25"/>
+    <tableColumn id="37" xr3:uid="{40241EEC-E88D-4A0C-B493-062B7F500182}" name="Prerequisites" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{B21C2D4B-1A24-4050-A8E0-997BCFB44AE8}" name="Work Location" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}" name="Table31013" displayName="Table31013" ref="A1:I32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}" name="Table31013" displayName="Table31013" ref="A1:I32" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:I32" xr:uid="{BADE214C-524C-4173-9535-0462A587B848}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{ADAD7CF3-9F65-47B1-86F1-BE3883188D10}" name="Role" dataDxfId="27"/>
-    <tableColumn id="31" xr3:uid="{1D7C1852-5EE8-43B9-A2D0-AFE5498F7C63}" name="Internship Level" dataDxfId="26"/>
-    <tableColumn id="32" xr3:uid="{C38FC37D-6B90-4DBC-8B22-30C73FB7E78F}" name="Internship Period" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{9C443B60-077D-430B-BA97-755EB594A1E1}" name="Division" dataDxfId="24"/>
-    <tableColumn id="34" xr3:uid="{C98D5E66-0F58-4CC1-BDF1-F0CD7D87CF9C}" name="Project Title" dataDxfId="23"/>
-    <tableColumn id="35" xr3:uid="{131629FC-1E47-4368-B7CD-85F89FF9D2BF}" name="Project Description" dataDxfId="22"/>
-    <tableColumn id="36" xr3:uid="{D65A7B37-B058-4C47-87D8-7038D5A150D3}" name="Learning Outcomes from Project" dataDxfId="21"/>
-    <tableColumn id="37" xr3:uid="{8294E7D5-FD11-4F40-A3FA-30B0AC6C73CF}" name="Prerequisites" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{068376EE-C48C-447A-9755-DE55ADB04FC5}" name="Work Location (FormSG)" dataDxfId="19"/>
+    <tableColumn id="33" xr3:uid="{ADAD7CF3-9F65-47B1-86F1-BE3883188D10}" name="Role" dataDxfId="20"/>
+    <tableColumn id="31" xr3:uid="{1D7C1852-5EE8-43B9-A2D0-AFE5498F7C63}" name="Internship Level" dataDxfId="19"/>
+    <tableColumn id="32" xr3:uid="{C38FC37D-6B90-4DBC-8B22-30C73FB7E78F}" name="Internship Period" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{9C443B60-077D-430B-BA97-755EB594A1E1}" name="Division" dataDxfId="17"/>
+    <tableColumn id="34" xr3:uid="{C98D5E66-0F58-4CC1-BDF1-F0CD7D87CF9C}" name="Project Title" dataDxfId="16"/>
+    <tableColumn id="35" xr3:uid="{131629FC-1E47-4368-B7CD-85F89FF9D2BF}" name="Project Description" dataDxfId="15"/>
+    <tableColumn id="36" xr3:uid="{D65A7B37-B058-4C47-87D8-7038D5A150D3}" name="Learning Outcomes from Project" dataDxfId="14"/>
+    <tableColumn id="37" xr3:uid="{8294E7D5-FD11-4F40-A3FA-30B0AC6C73CF}" name="Prerequisites" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{068376EE-C48C-447A-9755-DE55ADB04FC5}" name="Work Location (FormSG)" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}" name="Table31016" displayName="Table31016" ref="A1:I5" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}" name="Table31016" displayName="Table31016" ref="A1:I5" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I5" xr:uid="{B559FA25-9AE4-4675-A88F-7206D7394B54}"/>
   <tableColumns count="9">
-    <tableColumn id="33" xr3:uid="{DA95D0AA-FB62-4B70-A800-88F930027C34}" name="Role" dataDxfId="16"/>
-    <tableColumn id="31" xr3:uid="{8E2FF570-713F-4DB5-988B-05A7C30FAFB3}" name="Internship Level" dataDxfId="15"/>
-    <tableColumn id="32" xr3:uid="{464B50A7-A89C-4909-B713-BF4F1C4135B4}" name="Internship Period" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{78F66A91-700B-442F-A6BD-6CE3D5107534}" name="Division" dataDxfId="13"/>
-    <tableColumn id="34" xr3:uid="{B458784E-378C-4CCD-BD09-D53D5B77407A}" name="Project Title" dataDxfId="12"/>
-    <tableColumn id="35" xr3:uid="{30B3A4A5-74EB-4F83-B8AD-928A5AF98DCE}" name="Project Description" dataDxfId="11"/>
-    <tableColumn id="36" xr3:uid="{E55669FF-2098-4AD3-ABA2-9B535069A7B9}" name="Learning Outcomes from Project" dataDxfId="10"/>
-    <tableColumn id="37" xr3:uid="{65FC8008-BE3F-412D-BB33-14DEC1FAA16B}" name="Prerequisites" dataDxfId="9"/>
-    <tableColumn id="1" xr3:uid="{D8FD8DAE-DD25-4B67-8930-CC786B7B5D99}" name="Work Location" dataDxfId="8"/>
+    <tableColumn id="33" xr3:uid="{DA95D0AA-FB62-4B70-A800-88F930027C34}" name="Role" dataDxfId="8"/>
+    <tableColumn id="31" xr3:uid="{8E2FF570-713F-4DB5-988B-05A7C30FAFB3}" name="Internship Level" dataDxfId="7"/>
+    <tableColumn id="32" xr3:uid="{464B50A7-A89C-4909-B713-BF4F1C4135B4}" name="Internship Period" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{78F66A91-700B-442F-A6BD-6CE3D5107534}" name="Division" dataDxfId="5"/>
+    <tableColumn id="34" xr3:uid="{B458784E-378C-4CCD-BD09-D53D5B77407A}" name="Project Title" dataDxfId="4"/>
+    <tableColumn id="35" xr3:uid="{30B3A4A5-74EB-4F83-B8AD-928A5AF98DCE}" name="Project Description" dataDxfId="3"/>
+    <tableColumn id="36" xr3:uid="{E55669FF-2098-4AD3-ABA2-9B535069A7B9}" name="Learning Outcomes from Project" dataDxfId="2"/>
+    <tableColumn id="37" xr3:uid="{65FC8008-BE3F-412D-BB33-14DEC1FAA16B}" name="Prerequisites" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D8FD8DAE-DD25-4B67-8930-CC786B7B5D99}" name="Work Location" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5064,7 +5126,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5170,7 +5232,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5312,7 +5374,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5321,11 +5383,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C9D4452-6B68-410D-A94F-ED003A775C8F}">
   <dimension ref="B1:B22"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="8.7109375" style="5"/>
     <col min="2" max="2" width="99" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="5"/>
+    <col min="3" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" s="2" customFormat="1" ht="21">
@@ -5335,34 +5397,34 @@
     </row>
     <row r="2" spans="2:2" s="2" customFormat="1" ht="13.5" customHeight="1">
       <c r="B2" s="3" t="s">
-        <v>1021</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="360" customHeight="1">
       <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="7" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="8" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="9" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="10" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="11" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="12" spans="2:2" ht="14.5" customHeight="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="7" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="8" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="9" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="10" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="11" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="12" spans="2:2" ht="14.45" customHeight="1"/>
     <row r="13" spans="2:2" ht="15" customHeight="1"/>
-    <row r="14" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="15" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="16" spans="2:2" ht="14.5" customHeight="1"/>
-    <row r="17" ht="14.5" customHeight="1"/>
-    <row r="18" ht="14.5" customHeight="1"/>
-    <row r="19" ht="14.5" customHeight="1"/>
-    <row r="21" ht="14.5" customHeight="1"/>
+    <row r="14" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="15" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="16" spans="2:2" ht="14.45" customHeight="1"/>
+    <row r="17" ht="14.45" customHeight="1"/>
+    <row r="18" ht="14.45" customHeight="1"/>
+    <row r="19" ht="14.45" customHeight="1"/>
+    <row r="21" ht="14.45" customHeight="1"/>
     <row r="22" ht="69" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -5374,2604 +5436,2604 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CB8B7AC-F5FC-46C4-BB11-51E2956519D3}">
   <dimension ref="A1:I89"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.1" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="46.81640625" style="7"/>
-    <col min="3" max="5" width="46.81640625" style="8"/>
-    <col min="7" max="7" width="46.81640625" style="7"/>
-    <col min="8" max="16384" width="46.81640625" style="8"/>
+    <col min="2" max="2" width="46.85546875" style="7"/>
+    <col min="3" max="5" width="46.85546875" style="8"/>
+    <col min="7" max="7" width="46.85546875" style="7"/>
+    <col min="8" max="16384" width="46.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35.15" customHeight="1">
+    <row r="1" spans="1:9" ht="35.1" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1020</v>
+        <v>57</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F26" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" t="s">
         <v>154</v>
-      </c>
-      <c r="G26" t="s">
-        <v>155</v>
-      </c>
-      <c r="H26" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="39.75" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E27" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="H27" t="s">
         <v>159</v>
       </c>
-      <c r="G27" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" t="s">
-        <v>156</v>
-      </c>
       <c r="I27" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.75" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H28" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.75" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H29" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.75" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H30" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.75" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G31" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H31" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.75" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G32" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H32" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I32" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="39.75" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G33" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H33" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="39.75" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G34" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H34" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="39.75" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F35" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G35" t="s">
+        <v>203</v>
+      </c>
+      <c r="H35" t="s">
         <v>199</v>
       </c>
-      <c r="G35" t="s">
-        <v>200</v>
-      </c>
-      <c r="H35" t="s">
-        <v>196</v>
-      </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="39.75" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G36" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H36" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I36" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="39.75" customHeight="1">
       <c r="A37" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G37" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H37" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I37" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="39.75" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G38" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H38" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="39.75" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G39" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H39" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="39.75" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G40" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H40" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="I40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="39.75" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G41" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H41" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="39.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G42" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="39.75" customHeight="1">
       <c r="A43" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G43" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H43" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="39.75" customHeight="1">
       <c r="A44" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H44" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="39.75" customHeight="1">
       <c r="A45" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G45" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H45" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I45" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="39.75" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G46" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I46" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="39.75" customHeight="1">
       <c r="A47" s="9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G47" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H47" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="I47" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="39.75" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G48" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H48" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="39.75" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G49" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="H49" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="39.75" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G50" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H50" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="I50" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="39.75" customHeight="1">
       <c r="A51" s="9" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G51" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H51" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I51" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="39.75" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G52" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H52" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I52" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="39.75" customHeight="1">
       <c r="A53" s="9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G53" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H53" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="I53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="39.75" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G54" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H54" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I54" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="39.75" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G55" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H55" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="39.75" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="H56" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="I56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="39.75" customHeight="1">
       <c r="A57" s="9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G57" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="I57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="39.75" customHeight="1">
       <c r="A58" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G58" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I58" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="39.75" customHeight="1">
       <c r="A59" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G59" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="H59" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="39.75" customHeight="1">
       <c r="A60" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G60" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H60" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="39.75" customHeight="1">
       <c r="A61" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G61" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H61" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="39.75" customHeight="1">
       <c r="A62" s="9" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G62" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H62" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="39.75" customHeight="1">
       <c r="A63" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G63" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H63" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="39.75" customHeight="1">
       <c r="A64" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G64" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H64" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="39.75" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G65" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H65" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="39.75" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G66" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H66" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="39.75" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G67" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H67" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="39.75" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G68" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H68" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I68" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="39.75" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G69" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="H69" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="I69" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="39.75" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G70" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H70" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="I70" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="39.75" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G71" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H71" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I71" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="39.75" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G72" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H72" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I72" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="39.75" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G73" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="H73" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="39.75" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G74" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H74" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I74" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="39.75" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G75" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H75" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="I75" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="39.75" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G76" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H76" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="I76" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="39.75" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G77" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="H77" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="I77" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="39.75" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G78" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="H78" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="39.75" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="39.75" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H80" s="12" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="39.75" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="39.75" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H82" s="12" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="39.75" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="39.75" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="H84" s="12" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="39.75" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="39.75" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="39.75" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="39.75" customHeight="1">
       <c r="A88" s="9" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="37.5" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="H89" s="12" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G90:I1048576 E1:G6 F7:G7 E8:G25 E30:F36 E26:F28">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7983,35 +8045,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CC78194-0EAE-4863-932E-620D6F9003D6}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="14.45"/>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8021,445 +8083,445 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="39.75" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="39.75" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="39.75" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F16" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>563</v>
-      </c>
       <c r="H16" s="9" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:H7 G9:H14 E8:G8 J10:J1048576 G17:H1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -8473,37 +8535,37 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="9" width="46.81640625" customWidth="1"/>
-    <col min="10" max="11" width="17.453125" customWidth="1"/>
+    <col min="1" max="9" width="46.85546875" customWidth="1"/>
+    <col min="10" max="11" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8513,31 +8575,31 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -8547,263 +8609,263 @@
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -8817,35 +8879,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2CB887-DB2F-4039-85A3-42E8AE0B7F48}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -8855,390 +8917,390 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="49.5" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="14.5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="14.45">
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:14" ht="14.5"/>
-    <row r="17" ht="14.5"/>
-    <row r="18" ht="14.5"/>
+    <row r="16" spans="1:14" ht="14.45"/>
+    <row r="17" ht="14.45"/>
+    <row r="18" ht="14.45"/>
   </sheetData>
   <conditionalFormatting sqref="E7:H13 E1:H4 F5:H6">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -9250,357 +9312,357 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E54D435-1138-4E19-BF53-70A1844CFEF0}">
   <dimension ref="A1:I112"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.45" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="61" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A2" s="22" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A3" s="22" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A6" s="22" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A7" s="22" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A8" s="22" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A9" s="22" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="I9" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A11" s="23" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="13" customFormat="1" ht="39.75" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="13" customFormat="1" ht="15" customHeight="1">
@@ -10092,17 +10154,17 @@
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="1:9" ht="23.5" customHeight="1">
+    <row r="111" spans="1:9" ht="23.45" customHeight="1">
       <c r="B111" s="13"/>
       <c r="F111" s="13"/>
     </row>
-    <row r="112" spans="1:9" ht="23.5" customHeight="1">
+    <row r="112" spans="1:9" ht="23.45" customHeight="1">
       <c r="B112" s="13"/>
       <c r="F112" s="13"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G6:G1048576 E1:E12">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -10113,761 +10175,791 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58BB3264-CF9E-43B5-AED5-B1522208F209}">
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="23.5" customHeight="1"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="23.45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="72.7265625" customWidth="1"/>
+    <col min="1" max="1" width="72.7109375" customWidth="1"/>
+    <col min="9" max="9" width="63.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="9" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="I2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="F3" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G3" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="I3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F4" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="G4" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="H4" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="I4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="F5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="G5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="I5" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.75" customHeight="1">
       <c r="A6" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E6" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F6" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G6" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H6" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1">
       <c r="A7" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="G7" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="H7" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.75" customHeight="1">
       <c r="A8" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F8" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G8" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="H8" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="I8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.75" customHeight="1">
       <c r="A9" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="F9" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="G9" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="H9" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="I9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.75" customHeight="1">
       <c r="A10" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F10" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="G10" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="H10" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.75" customHeight="1">
       <c r="A11" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E11" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F11" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="G11" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="H11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.75" customHeight="1">
       <c r="A12" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E12" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F12" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="G12" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H12" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="I12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1">
       <c r="A13" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H13" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1">
       <c r="A14" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E14" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="F14" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="G14" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="H14" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1">
       <c r="A15" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F15" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="G15" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="H15" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="I15" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1">
       <c r="A16" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E16" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F16" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="G16" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="H16" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="I16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E17" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F17" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="G17" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="H17" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="I17" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E18" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="F18" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="G18" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="H18" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G19" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="H19" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="I19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E20" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="F20" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="G20" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="H20" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="I20" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E21" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="F21" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="G21" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="H21" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="F22" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="G22" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="H22" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E23" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="F23" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="G23" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="H23" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="H24" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E25" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="F25" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="G25" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="H25" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="39.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>868</v>
+      </c>
+      <c r="B27" t="s">
+        <v>869</v>
+      </c>
+      <c r="C27" t="s">
+        <v>870</v>
+      </c>
+      <c r="D27" t="s">
+        <v>871</v>
+      </c>
+      <c r="E27" t="s">
+        <v>872</v>
+      </c>
+      <c r="F27" t="s">
+        <v>873</v>
+      </c>
+      <c r="G27" t="s">
+        <v>874</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="I27" t="s">
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -10881,38 +10973,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83D9A09-A0E5-4E5C-AE97-C199E23F008E}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
@@ -10922,31 +11014,31 @@
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1">
       <c r="A2" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="G2" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="H2" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
@@ -10956,872 +11048,872 @@
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1">
       <c r="A3" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E3" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="F3" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="G3" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="H3" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="I3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1">
       <c r="A4" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="H4" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1">
       <c r="A5" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G5" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="H5" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="I5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1">
       <c r="A6" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="H6" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1">
       <c r="A7" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E7" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F7" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="G7" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="H7" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="I7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1">
       <c r="A8" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F8" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G8" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="H8" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="39.75" customHeight="1">
       <c r="A9" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E9" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="F9" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="G9" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="H9" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="I9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="39.75" customHeight="1">
       <c r="A10" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E10" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="F10" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="G10" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="H10" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="I10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="39.75" customHeight="1">
       <c r="A11" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="F11" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="G11" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="H11" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="39.75" customHeight="1">
       <c r="A12" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="F12" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="G12" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="H12" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="I12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39.75" customHeight="1">
       <c r="A13" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="B13" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="G13" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="H13" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="39.75" customHeight="1">
       <c r="A14" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E14" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F14" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="G14" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="H14" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="39.75" customHeight="1">
       <c r="A15" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E15" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="F15" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="G15" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="H15" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="I15" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="39.75" customHeight="1">
       <c r="A16" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="F16" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="G16" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="H16" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E17" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
       <c r="F17" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="G17" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="H17" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
       <c r="I17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1">
       <c r="A18" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="H18" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="I18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1">
       <c r="A19" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
       <c r="F19" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="G19" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="H19" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1">
       <c r="A20" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="F20" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="G20" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="H20" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="I20" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1">
       <c r="A21" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="F21" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="G21" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c r="H21" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1">
       <c r="A22" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="B22" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="F22" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="G22" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="H22" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="I22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1">
       <c r="A23" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E23" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
       <c r="F23" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="G23" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="H23" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="I23" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1">
       <c r="A24" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F24" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="G24" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="H24" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="I24" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1">
       <c r="A25" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F25" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="G25" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="H25" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="I25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
       <c r="A26" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="F26" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
       <c r="G26" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="H26" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="39.75" customHeight="1">
       <c r="A27" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="F27" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="G27" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="H27" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="I27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="39.75" customHeight="1">
       <c r="A28" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E28" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F28" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="G28" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="H28" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="I28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="39.75" customHeight="1">
       <c r="A29" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="F29" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="G29" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="H29" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="I29" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="39.75" customHeight="1">
       <c r="A30" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E30" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="F30" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="G30" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="H30" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.75" customHeight="1">
       <c r="A31" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E31" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F31" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
       <c r="G31" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="H31" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39.75" customHeight="1">
       <c r="A32" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E32" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
       <c r="F32" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="H32" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -11835,160 +11927,160 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1732FC4-DAAC-4993-874D-9F36FC6B0102}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="46.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="46.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="69" customWidth="1"/>
-    <col min="9" max="9" width="76.26953125" customWidth="1"/>
+    <col min="9" max="9" width="76.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.75" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.75" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="39.75" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:G5">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -11998,15 +12090,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Status xmlns="fdedef4e-87e2-4000-8e15-674cde7c8b45">New</Status>
@@ -12016,6 +12099,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12257,39 +12349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{068544F8-3AE0-4EEF-90C6-5DD75B425137}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553F84EA-27AD-4FBD-9707-81276D747B07}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553F84EA-27AD-4FBD-9707-81276D747B07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fdedef4e-87e2-4000-8e15-674cde7c8b45"/>
-    <ds:schemaRef ds:uri="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{068544F8-3AE0-4EEF-90C6-5DD75B425137}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A57F35-6032-40B6-B658-A82B5AB99034}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="fdedef4e-87e2-4000-8e15-674cde7c8b45"/>
-    <ds:schemaRef ds:uri="ac9f22f5-36f4-4c3c-a6dd-2b7ae81e18c8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91A57F35-6032-40B6-B658-A82B5AB99034}"/>
 </file>